--- a/Supplementary_Table_S2_Spatial_Neighborhood_Enrichment.xlsx
+++ b/Supplementary_Table_S2_Spatial_Neighborhood_Enrichment.xlsx
@@ -14107,7 +14107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D379"/>
+  <dimension ref="A1:F379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14123,12 +14123,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>diff_score</t>
+          <t>diff_zscore</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>abs_diff_score</t>
+          <t>CLR_zscore</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>DII_zscore</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>abs_diff_zscore</t>
         </is>
       </c>
     </row>
@@ -14147,6 +14157,12 @@
         <v>18.62798497350559</v>
       </c>
       <c r="D2" t="n">
+        <v>19.28589084749682</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6579058739912214</v>
+      </c>
+      <c r="F2" t="n">
         <v>18.62798497350559</v>
       </c>
     </row>
@@ -14165,6 +14181,12 @@
         <v>-14.57193561559907</v>
       </c>
       <c r="D3" t="n">
+        <v>21.6123618795777</v>
+      </c>
+      <c r="E3" t="n">
+        <v>36.18429749517677</v>
+      </c>
+      <c r="F3" t="n">
         <v>14.57193561559907</v>
       </c>
     </row>
@@ -14183,6 +14205,12 @@
         <v>7.626557062710149</v>
       </c>
       <c r="D4" t="n">
+        <v>-5.304528803166527</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-12.93108586587668</v>
+      </c>
+      <c r="F4" t="n">
         <v>7.626557062710149</v>
       </c>
     </row>
@@ -14201,6 +14229,12 @@
         <v>5.942974144096787</v>
       </c>
       <c r="D5" t="n">
+        <v>5.728254070572152</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.2147200735246355</v>
+      </c>
+      <c r="F5" t="n">
         <v>5.942974144096787</v>
       </c>
     </row>
@@ -14219,6 +14253,12 @@
         <v>5.884383858946547</v>
       </c>
       <c r="D6" t="n">
+        <v>12.0513820237007</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6.166998164754149</v>
+      </c>
+      <c r="F6" t="n">
         <v>5.884383858946547</v>
       </c>
     </row>
@@ -14237,6 +14277,12 @@
         <v>4.696067405726756</v>
       </c>
       <c r="D7" t="n">
+        <v>-6.185917720800211</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-10.88198512652697</v>
+      </c>
+      <c r="F7" t="n">
         <v>4.696067405726756</v>
       </c>
     </row>
@@ -14255,6 +14301,12 @@
         <v>-4.384907634585984</v>
       </c>
       <c r="D8" t="n">
+        <v>8.77123289227891</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13.15614052686489</v>
+      </c>
+      <c r="F8" t="n">
         <v>4.384907634585984</v>
       </c>
     </row>
@@ -14273,6 +14325,12 @@
         <v>-4.122621822918719</v>
       </c>
       <c r="D9" t="n">
+        <v>2.409535361912261</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6.532157184830979</v>
+      </c>
+      <c r="F9" t="n">
         <v>4.122621822918719</v>
       </c>
     </row>
@@ -14291,6 +14349,12 @@
         <v>-4.023566260311713</v>
       </c>
       <c r="D10" t="n">
+        <v>-3.200757561485313</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.8228086988264002</v>
+      </c>
+      <c r="F10" t="n">
         <v>4.023566260311713</v>
       </c>
     </row>
@@ -14309,6 +14373,12 @@
         <v>3.834376216523979</v>
       </c>
       <c r="D11" t="n">
+        <v>4.994094936172794</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.159718719648815</v>
+      </c>
+      <c r="F11" t="n">
         <v>3.834376216523979</v>
       </c>
     </row>
@@ -14327,6 +14397,12 @@
         <v>3.72714487595085</v>
       </c>
       <c r="D12" t="n">
+        <v>-3.126366207097053</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-6.853511083047903</v>
+      </c>
+      <c r="F12" t="n">
         <v>3.72714487595085</v>
       </c>
     </row>
@@ -14345,6 +14421,12 @@
         <v>3.610156323877376</v>
       </c>
       <c r="D13" t="n">
+        <v>-2.75194703502145</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-6.362103358898826</v>
+      </c>
+      <c r="F13" t="n">
         <v>3.610156323877376</v>
       </c>
     </row>
@@ -14363,6 +14445,12 @@
         <v>3.407689377945347</v>
       </c>
       <c r="D14" t="n">
+        <v>-0.5724243543376967</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-3.980113732283043</v>
+      </c>
+      <c r="F14" t="n">
         <v>3.407689377945347</v>
       </c>
     </row>
@@ -14381,6 +14469,12 @@
         <v>-3.357133368964189</v>
       </c>
       <c r="D15" t="n">
+        <v>-0.3881092098544876</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.969024159109702</v>
+      </c>
+      <c r="F15" t="n">
         <v>3.357133368964189</v>
       </c>
     </row>
@@ -14399,6 +14493,12 @@
         <v>3.105941193724029</v>
       </c>
       <c r="D16" t="n">
+        <v>4.946027052765205</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.840085859041176</v>
+      </c>
+      <c r="F16" t="n">
         <v>3.105941193724029</v>
       </c>
     </row>
@@ -14417,6 +14517,12 @@
         <v>-3.069153788911562</v>
       </c>
       <c r="D17" t="n">
+        <v>-4.866412216948946</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-1.797258428037385</v>
+      </c>
+      <c r="F17" t="n">
         <v>3.069153788911562</v>
       </c>
     </row>
@@ -14435,6 +14541,12 @@
         <v>2.948971608292649</v>
       </c>
       <c r="D18" t="n">
+        <v>-3.489761437724258</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-6.438733046016907</v>
+      </c>
+      <c r="F18" t="n">
         <v>2.948971608292649</v>
       </c>
     </row>
@@ -14453,6 +14565,12 @@
         <v>2.824159199516854</v>
       </c>
       <c r="D19" t="n">
+        <v>-3.557733576522371</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-6.381892776039225</v>
+      </c>
+      <c r="F19" t="n">
         <v>2.824159199516854</v>
       </c>
     </row>
@@ -14471,6 +14589,12 @@
         <v>-2.46812525583109</v>
       </c>
       <c r="D20" t="n">
+        <v>-2.976100436011116</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.5079751801800266</v>
+      </c>
+      <c r="F20" t="n">
         <v>2.46812525583109</v>
       </c>
     </row>
@@ -14489,6 +14613,12 @@
         <v>2.444671496891467</v>
       </c>
       <c r="D21" t="n">
+        <v>-1.824789577257808</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-4.269461074149275</v>
+      </c>
+      <c r="F21" t="n">
         <v>2.444671496891467</v>
       </c>
     </row>
@@ -14507,6 +14637,12 @@
         <v>2.425858434747963</v>
       </c>
       <c r="D22" t="n">
+        <v>-1.152909826512898</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-3.578768261260861</v>
+      </c>
+      <c r="F22" t="n">
         <v>2.425858434747963</v>
       </c>
     </row>
@@ -14525,6 +14661,12 @@
         <v>2.383271596082799</v>
       </c>
       <c r="D23" t="n">
+        <v>6.138651089884801</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3.755379493802002</v>
+      </c>
+      <c r="F23" t="n">
         <v>2.383271596082799</v>
       </c>
     </row>
@@ -14543,6 +14685,12 @@
         <v>2.053646720097159</v>
       </c>
       <c r="D24" t="n">
+        <v>0.752139276626182</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.301507443470977</v>
+      </c>
+      <c r="F24" t="n">
         <v>2.053646720097159</v>
       </c>
     </row>
@@ -14561,6 +14709,12 @@
         <v>-1.994305996502776</v>
       </c>
       <c r="D25" t="n">
+        <v>-1.307734909582013</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.686571086920763</v>
+      </c>
+      <c r="F25" t="n">
         <v>1.994305996502776</v>
       </c>
     </row>
@@ -14579,6 +14733,12 @@
         <v>1.920507241767916</v>
       </c>
       <c r="D26" t="n">
+        <v>-0.1555492984431035</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-2.07605654021102</v>
+      </c>
+      <c r="F26" t="n">
         <v>1.920507241767916</v>
       </c>
     </row>
@@ -14597,6 +14757,12 @@
         <v>1.904637558433459</v>
       </c>
       <c r="D27" t="n">
+        <v>2.956700853320454</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.052063294886994</v>
+      </c>
+      <c r="F27" t="n">
         <v>1.904637558433459</v>
       </c>
     </row>
@@ -14615,6 +14781,12 @@
         <v>1.888055632892487</v>
       </c>
       <c r="D28" t="n">
+        <v>0.9153121288304785</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.9727435040620084</v>
+      </c>
+      <c r="F28" t="n">
         <v>1.888055632892487</v>
       </c>
     </row>
@@ -14633,6 +14805,12 @@
         <v>-1.883667346182129</v>
       </c>
       <c r="D29" t="n">
+        <v>-1.902158534784938</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.01849118860280891</v>
+      </c>
+      <c r="F29" t="n">
         <v>1.883667346182129</v>
       </c>
     </row>
@@ -14651,6 +14829,12 @@
         <v>-1.870639496890939</v>
       </c>
       <c r="D30" t="n">
+        <v>1.856704966486175</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.727344463377113</v>
+      </c>
+      <c r="F30" t="n">
         <v>1.870639496890939</v>
       </c>
     </row>
@@ -14669,6 +14853,12 @@
         <v>-1.823256786487623</v>
       </c>
       <c r="D31" t="n">
+        <v>0.3678677503861614</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.191124536873784</v>
+      </c>
+      <c r="F31" t="n">
         <v>1.823256786487623</v>
       </c>
     </row>
@@ -14687,6 +14877,12 @@
         <v>-1.809222489730823</v>
       </c>
       <c r="D32" t="n">
+        <v>-1.431648494075441</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.3775739956553821</v>
+      </c>
+      <c r="F32" t="n">
         <v>1.809222489730823</v>
       </c>
     </row>
@@ -14705,6 +14901,12 @@
         <v>-1.731629941300663</v>
       </c>
       <c r="D33" t="n">
+        <v>1.825661680278148</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.557291621578812</v>
+      </c>
+      <c r="F33" t="n">
         <v>1.731629941300663</v>
       </c>
     </row>
@@ -14723,6 +14925,12 @@
         <v>-1.677023335890954</v>
       </c>
       <c r="D34" t="n">
+        <v>-1.480711909728587</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.1963114261623669</v>
+      </c>
+      <c r="F34" t="n">
         <v>1.677023335890954</v>
       </c>
     </row>
@@ -14741,6 +14949,12 @@
         <v>-1.560190282920239</v>
       </c>
       <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.560190282920239</v>
+      </c>
+      <c r="F35" t="n">
         <v>1.560190282920239</v>
       </c>
     </row>
@@ -14759,6 +14973,12 @@
         <v>-1.556751936482828</v>
       </c>
       <c r="D36" t="n">
+        <v>1.288630652947623</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2.845382589430451</v>
+      </c>
+      <c r="F36" t="n">
         <v>1.556751936482828</v>
       </c>
     </row>
@@ -14777,6 +14997,12 @@
         <v>1.553956793691543</v>
       </c>
       <c r="D37" t="n">
+        <v>1.435501831833245</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.1184549618582975</v>
+      </c>
+      <c r="F37" t="n">
         <v>1.553956793691543</v>
       </c>
     </row>
@@ -14795,6 +15021,12 @@
         <v>1.522129583779475</v>
       </c>
       <c r="D38" t="n">
+        <v>-0.2955071864572144</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-1.817636770236689</v>
+      </c>
+      <c r="F38" t="n">
         <v>1.522129583779475</v>
       </c>
     </row>
@@ -14813,6 +15045,12 @@
         <v>1.502172093722123</v>
       </c>
       <c r="D39" t="n">
+        <v>-0.2074287657634153</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-1.709600859485539</v>
+      </c>
+      <c r="F39" t="n">
         <v>1.502172093722123</v>
       </c>
     </row>
@@ -14831,6 +15069,12 @@
         <v>-1.499414132620316</v>
       </c>
       <c r="D40" t="n">
+        <v>-0.3076728201393868</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.191741312480929</v>
+      </c>
+      <c r="F40" t="n">
         <v>1.499414132620316</v>
       </c>
     </row>
@@ -14849,6 +15093,12 @@
         <v>-1.484207664188687</v>
       </c>
       <c r="D41" t="n">
+        <v>-1.294760406770407</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.1894472574182794</v>
+      </c>
+      <c r="F41" t="n">
         <v>1.484207664188687</v>
       </c>
     </row>
@@ -14867,6 +15117,12 @@
         <v>-1.478584837652681</v>
       </c>
       <c r="D42" t="n">
+        <v>-0.8636092704579231</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6149755671947577</v>
+      </c>
+      <c r="F42" t="n">
         <v>1.478584837652681</v>
       </c>
     </row>
@@ -14885,6 +15141,12 @@
         <v>-1.474363208164155</v>
       </c>
       <c r="D43" t="n">
+        <v>-1.248103309460101</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.2262598987040547</v>
+      </c>
+      <c r="F43" t="n">
         <v>1.474363208164155</v>
       </c>
     </row>
@@ -14903,6 +15165,12 @@
         <v>-1.469824846123662</v>
       </c>
       <c r="D44" t="n">
+        <v>0.201321256415611</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.671146102539273</v>
+      </c>
+      <c r="F44" t="n">
         <v>1.469824846123662</v>
       </c>
     </row>
@@ -14921,6 +15189,12 @@
         <v>-1.447608106765537</v>
       </c>
       <c r="D45" t="n">
+        <v>-1.101955290351817</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.34565281641372</v>
+      </c>
+      <c r="F45" t="n">
         <v>1.447608106765537</v>
       </c>
     </row>
@@ -14939,6 +15213,12 @@
         <v>-1.445757235264453</v>
       </c>
       <c r="D46" t="n">
+        <v>-2.33768344835943</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.8919262130949769</v>
+      </c>
+      <c r="F46" t="n">
         <v>1.445757235264453</v>
       </c>
     </row>
@@ -14957,6 +15237,12 @@
         <v>1.435228928515902</v>
       </c>
       <c r="D47" t="n">
+        <v>1.181177895950007</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.2540510325658955</v>
+      </c>
+      <c r="F47" t="n">
         <v>1.435228928515902</v>
       </c>
     </row>
@@ -14975,6 +15261,12 @@
         <v>-1.395497330436989</v>
       </c>
       <c r="D48" t="n">
+        <v>0.07034514826618521</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.465842478703174</v>
+      </c>
+      <c r="F48" t="n">
         <v>1.395497330436989</v>
       </c>
     </row>
@@ -14993,6 +15285,12 @@
         <v>-1.386012283962798</v>
       </c>
       <c r="D49" t="n">
+        <v>-1.828792925096621</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.4427806411338226</v>
+      </c>
+      <c r="F49" t="n">
         <v>1.386012283962798</v>
       </c>
     </row>
@@ -15011,6 +15309,12 @@
         <v>1.360076210247489</v>
       </c>
       <c r="D50" t="n">
+        <v>1.54504446989038</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.1849682596428905</v>
+      </c>
+      <c r="F50" t="n">
         <v>1.360076210247489</v>
       </c>
     </row>
@@ -15029,6 +15333,12 @@
         <v>1.352516627341192</v>
       </c>
       <c r="D51" t="n">
+        <v>1.268942094917976</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.08357453242321596</v>
+      </c>
+      <c r="F51" t="n">
         <v>1.352516627341192</v>
       </c>
     </row>
@@ -15047,6 +15357,12 @@
         <v>1.289894466736696</v>
       </c>
       <c r="D52" t="n">
+        <v>1.324299576485415</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.03440510974871936</v>
+      </c>
+      <c r="F52" t="n">
         <v>1.289894466736696</v>
       </c>
     </row>
@@ -15065,6 +15381,12 @@
         <v>-1.278934305080432</v>
       </c>
       <c r="D53" t="n">
+        <v>-0.02032320645817084</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1.258611098622261</v>
+      </c>
+      <c r="F53" t="n">
         <v>1.278934305080432</v>
       </c>
     </row>
@@ -15083,6 +15405,12 @@
         <v>-1.247194339923392</v>
       </c>
       <c r="D54" t="n">
+        <v>-0.1177746634879818</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.129419676435411</v>
+      </c>
+      <c r="F54" t="n">
         <v>1.247194339923392</v>
       </c>
     </row>
@@ -15101,6 +15429,12 @@
         <v>1.245771204163634</v>
       </c>
       <c r="D55" t="n">
+        <v>2.235720229143634</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.98994902498</v>
+      </c>
+      <c r="F55" t="n">
         <v>1.245771204163634</v>
       </c>
     </row>
@@ -15119,6 +15453,12 @@
         <v>1.226785578768929</v>
       </c>
       <c r="D56" t="n">
+        <v>0.2121112278673269</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-1.014674350901602</v>
+      </c>
+      <c r="F56" t="n">
         <v>1.226785578768929</v>
       </c>
     </row>
@@ -15137,6 +15477,12 @@
         <v>-1.215417818866367</v>
       </c>
       <c r="D57" t="n">
+        <v>-0.3443773888066152</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.8710404300597515</v>
+      </c>
+      <c r="F57" t="n">
         <v>1.215417818866367</v>
       </c>
     </row>
@@ -15155,6 +15501,12 @@
         <v>-1.20728704265501</v>
       </c>
       <c r="D58" t="n">
+        <v>-0.2546711472307466</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.9526158954242637</v>
+      </c>
+      <c r="F58" t="n">
         <v>1.20728704265501</v>
       </c>
     </row>
@@ -15173,6 +15525,12 @@
         <v>-1.182289412772049</v>
       </c>
       <c r="D59" t="n">
+        <v>-0.9089035349523382</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.2733858778197111</v>
+      </c>
+      <c r="F59" t="n">
         <v>1.182289412772049</v>
       </c>
     </row>
@@ -15191,6 +15549,12 @@
         <v>1.164934184069615</v>
       </c>
       <c r="D60" t="n">
+        <v>-1.960557910078554</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-3.125492094148169</v>
+      </c>
+      <c r="F60" t="n">
         <v>1.164934184069615</v>
       </c>
     </row>
@@ -15209,6 +15573,12 @@
         <v>-1.158922646011039</v>
       </c>
       <c r="D61" t="n">
+        <v>-1.021779235362615</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.1371434106484235</v>
+      </c>
+      <c r="F61" t="n">
         <v>1.158922646011039</v>
       </c>
     </row>
@@ -15229,6 +15599,12 @@
       <c r="D62" t="n">
         <v>1.119710568039495</v>
       </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.119710568039495</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -15245,6 +15621,12 @@
         <v>-1.081559313716741</v>
       </c>
       <c r="D63" t="n">
+        <v>-1.159687175467042</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.07812786175030091</v>
+      </c>
+      <c r="F63" t="n">
         <v>1.081559313716741</v>
       </c>
     </row>
@@ -15263,6 +15645,12 @@
         <v>-1.07962839105735</v>
       </c>
       <c r="D64" t="n">
+        <v>0.5601418899052071</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.639770280962557</v>
+      </c>
+      <c r="F64" t="n">
         <v>1.07962839105735</v>
       </c>
     </row>
@@ -15281,6 +15669,12 @@
         <v>1.078387591684663</v>
       </c>
       <c r="D65" t="n">
+        <v>-0.1212721671266534</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-1.199659758811316</v>
+      </c>
+      <c r="F65" t="n">
         <v>1.078387591684663</v>
       </c>
     </row>
@@ -15299,6 +15693,12 @@
         <v>-1.076950115347908</v>
       </c>
       <c r="D66" t="n">
+        <v>-0.9646834306343388</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.1122666847135692</v>
+      </c>
+      <c r="F66" t="n">
         <v>1.076950115347908</v>
       </c>
     </row>
@@ -15317,6 +15717,12 @@
         <v>1.067990516844423</v>
       </c>
       <c r="D67" t="n">
+        <v>0.9443261719534258</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-0.1236643448909977</v>
+      </c>
+      <c r="F67" t="n">
         <v>1.067990516844423</v>
       </c>
     </row>
@@ -15335,6 +15741,12 @@
         <v>-1.065832906280778</v>
       </c>
       <c r="D68" t="n">
+        <v>5.686553923225935</v>
+      </c>
+      <c r="E68" t="n">
+        <v>6.752386829506713</v>
+      </c>
+      <c r="F68" t="n">
         <v>1.065832906280778</v>
       </c>
     </row>
@@ -15353,6 +15765,12 @@
         <v>1.065774056521291</v>
       </c>
       <c r="D69" t="n">
+        <v>0.09117337177117817</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-0.9746006847501123</v>
+      </c>
+      <c r="F69" t="n">
         <v>1.065774056521291</v>
       </c>
     </row>
@@ -15371,6 +15789,12 @@
         <v>-1.06309257348417</v>
       </c>
       <c r="D70" t="n">
+        <v>-0.8958949940088233</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.1671975794753468</v>
+      </c>
+      <c r="F70" t="n">
         <v>1.06309257348417</v>
       </c>
     </row>
@@ -15389,6 +15813,12 @@
         <v>1.053550114410913</v>
       </c>
       <c r="D71" t="n">
+        <v>1.291305938640908</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.2377558242299957</v>
+      </c>
+      <c r="F71" t="n">
         <v>1.053550114410913</v>
       </c>
     </row>
@@ -15407,6 +15837,12 @@
         <v>1.038659392483716</v>
       </c>
       <c r="D72" t="n">
+        <v>1.054130917496123</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.01547152501240749</v>
+      </c>
+      <c r="F72" t="n">
         <v>1.038659392483716</v>
       </c>
     </row>
@@ -15425,6 +15861,12 @@
         <v>1.005232262261195</v>
       </c>
       <c r="D73" t="n">
+        <v>-2.966209926395935</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-3.971442188657131</v>
+      </c>
+      <c r="F73" t="n">
         <v>1.005232262261195</v>
       </c>
     </row>
@@ -15443,6 +15885,12 @@
         <v>-0.9857810924400674</v>
       </c>
       <c r="D74" t="n">
+        <v>-0.9936417795561517</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-0.007860687116084288</v>
+      </c>
+      <c r="F74" t="n">
         <v>0.9857810924400674</v>
       </c>
     </row>
@@ -15461,6 +15909,12 @@
         <v>0.9794895395155152</v>
       </c>
       <c r="D75" t="n">
+        <v>-0.2412884668094421</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-1.220778006324957</v>
+      </c>
+      <c r="F75" t="n">
         <v>0.9794895395155152</v>
       </c>
     </row>
@@ -15479,6 +15933,12 @@
         <v>-0.9707165974964478</v>
       </c>
       <c r="D76" t="n">
+        <v>-0.2591150926287996</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.7116015048676482</v>
+      </c>
+      <c r="F76" t="n">
         <v>0.9707165974964478</v>
       </c>
     </row>
@@ -15497,6 +15957,12 @@
         <v>0.9697196071784288</v>
       </c>
       <c r="D77" t="n">
+        <v>0.4688210660190596</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-0.5008985411593692</v>
+      </c>
+      <c r="F77" t="n">
         <v>0.9697196071784288</v>
       </c>
     </row>
@@ -15515,6 +15981,12 @@
         <v>0.9659499873913828</v>
       </c>
       <c r="D78" t="n">
+        <v>-0.2013573813482583</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-1.167307368739641</v>
+      </c>
+      <c r="F78" t="n">
         <v>0.9659499873913828</v>
       </c>
     </row>
@@ -15533,6 +16005,12 @@
         <v>-0.9340007447481006</v>
       </c>
       <c r="D79" t="n">
+        <v>0.04562935787982413</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.9796301026279247</v>
+      </c>
+      <c r="F79" t="n">
         <v>0.9340007447481006</v>
       </c>
     </row>
@@ -15551,6 +16029,12 @@
         <v>0.9317584128183501</v>
       </c>
       <c r="D80" t="n">
+        <v>0.7053889405140624</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-0.2263694723042877</v>
+      </c>
+      <c r="F80" t="n">
         <v>0.9317584128183501</v>
       </c>
     </row>
@@ -15569,6 +16053,12 @@
         <v>-0.9287961511217067</v>
       </c>
       <c r="D81" t="n">
+        <v>-1.334467558279214</v>
+      </c>
+      <c r="E81" t="n">
+        <v>-0.4056714071575072</v>
+      </c>
+      <c r="F81" t="n">
         <v>0.9287961511217067</v>
       </c>
     </row>
@@ -15587,6 +16077,12 @@
         <v>0.9197438774669886</v>
       </c>
       <c r="D82" t="n">
+        <v>0.7666442389235782</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-0.1530996385434104</v>
+      </c>
+      <c r="F82" t="n">
         <v>0.9197438774669886</v>
       </c>
     </row>
@@ -15605,6 +16101,12 @@
         <v>-0.9157876822909692</v>
       </c>
       <c r="D83" t="n">
+        <v>-0.3001159808576329</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.6156717014333364</v>
+      </c>
+      <c r="F83" t="n">
         <v>0.9157876822909692</v>
       </c>
     </row>
@@ -15623,6 +16125,12 @@
         <v>0.9097117985068792</v>
       </c>
       <c r="D84" t="n">
+        <v>0.638183398986762</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-0.2715283995201171</v>
+      </c>
+      <c r="F84" t="n">
         <v>0.9097117985068792</v>
       </c>
     </row>
@@ -15641,6 +16149,12 @@
         <v>-0.9022459339429264</v>
       </c>
       <c r="D85" t="n">
+        <v>-1.194266104623414</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-0.292020170680488</v>
+      </c>
+      <c r="F85" t="n">
         <v>0.9022459339429264</v>
       </c>
     </row>
@@ -15659,6 +16173,12 @@
         <v>0.896141685873018</v>
       </c>
       <c r="D86" t="n">
+        <v>-0.8007410407093554</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-1.696882726582373</v>
+      </c>
+      <c r="F86" t="n">
         <v>0.896141685873018</v>
       </c>
     </row>
@@ -15677,6 +16197,12 @@
         <v>0.8772699989754624</v>
       </c>
       <c r="D87" t="n">
+        <v>8.848596930409618</v>
+      </c>
+      <c r="E87" t="n">
+        <v>7.971326931434156</v>
+      </c>
+      <c r="F87" t="n">
         <v>0.8772699989754624</v>
       </c>
     </row>
@@ -15695,6 +16221,12 @@
         <v>0.87557798577853</v>
       </c>
       <c r="D88" t="n">
+        <v>0.06989814441713714</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-0.8056798413613928</v>
+      </c>
+      <c r="F88" t="n">
         <v>0.87557798577853</v>
       </c>
     </row>
@@ -15713,6 +16245,12 @@
         <v>0.866291400124461</v>
       </c>
       <c r="D89" t="n">
+        <v>6.532690514748539</v>
+      </c>
+      <c r="E89" t="n">
+        <v>5.666399114624078</v>
+      </c>
+      <c r="F89" t="n">
         <v>0.866291400124461</v>
       </c>
     </row>
@@ -15731,6 +16269,12 @@
         <v>-0.8384010400934463</v>
       </c>
       <c r="D90" t="n">
+        <v>0.8423590026969481</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1.680760042790394</v>
+      </c>
+      <c r="F90" t="n">
         <v>0.8384010400934463</v>
       </c>
     </row>
@@ -15749,6 +16293,12 @@
         <v>-0.8281169618033231</v>
       </c>
       <c r="D91" t="n">
+        <v>1.55430221276484</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2.382419174568163</v>
+      </c>
+      <c r="F91" t="n">
         <v>0.8281169618033231</v>
       </c>
     </row>
@@ -15767,6 +16317,12 @@
         <v>-0.8253241186715369</v>
       </c>
       <c r="D92" t="n">
+        <v>-1.045347682366724</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-0.2200235636951874</v>
+      </c>
+      <c r="F92" t="n">
         <v>0.8253241186715369</v>
       </c>
     </row>
@@ -15785,6 +16341,12 @@
         <v>0.8220536379605298</v>
       </c>
       <c r="D93" t="n">
+        <v>0.6629730929242194</v>
+      </c>
+      <c r="E93" t="n">
+        <v>-0.1590805450363104</v>
+      </c>
+      <c r="F93" t="n">
         <v>0.8220536379605298</v>
       </c>
     </row>
@@ -15803,6 +16365,12 @@
         <v>-0.8197561707020092</v>
       </c>
       <c r="D94" t="n">
+        <v>0.4790050167396301</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.298761187441639</v>
+      </c>
+      <c r="F94" t="n">
         <v>0.8197561707020092</v>
       </c>
     </row>
@@ -15821,6 +16389,12 @@
         <v>0.8182356069077116</v>
       </c>
       <c r="D95" t="n">
+        <v>0.5350775603599305</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-0.2831580465477811</v>
+      </c>
+      <c r="F95" t="n">
         <v>0.8182356069077116</v>
       </c>
     </row>
@@ -15839,6 +16413,12 @@
         <v>0.8045600195852733</v>
       </c>
       <c r="D96" t="n">
+        <v>4.826854003242958</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4.022293983657685</v>
+      </c>
+      <c r="F96" t="n">
         <v>0.8045600195852733</v>
       </c>
     </row>
@@ -15857,6 +16437,12 @@
         <v>0.8008446535096154</v>
       </c>
       <c r="D97" t="n">
+        <v>1.96035545670715</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1.159510803197535</v>
+      </c>
+      <c r="F97" t="n">
         <v>0.8008446535096154</v>
       </c>
     </row>
@@ -15875,6 +16461,12 @@
         <v>-0.7986973773528059</v>
       </c>
       <c r="D98" t="n">
+        <v>-0.2019550241402965</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.5967423532125093</v>
+      </c>
+      <c r="F98" t="n">
         <v>0.7986973773528059</v>
       </c>
     </row>
@@ -15893,6 +16485,12 @@
         <v>0.7984474143810311</v>
       </c>
       <c r="D99" t="n">
+        <v>0.7045001941038341</v>
+      </c>
+      <c r="E99" t="n">
+        <v>-0.09394722027719693</v>
+      </c>
+      <c r="F99" t="n">
         <v>0.7984474143810311</v>
       </c>
     </row>
@@ -15911,6 +16509,12 @@
         <v>0.7905850423632973</v>
       </c>
       <c r="D100" t="n">
+        <v>0.578073152342393</v>
+      </c>
+      <c r="E100" t="n">
+        <v>-0.2125118900209043</v>
+      </c>
+      <c r="F100" t="n">
         <v>0.7905850423632973</v>
       </c>
     </row>
@@ -15929,6 +16533,12 @@
         <v>0.7888903385175713</v>
       </c>
       <c r="D101" t="n">
+        <v>-0.4590577760619662</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-1.247948114579537</v>
+      </c>
+      <c r="F101" t="n">
         <v>0.7888903385175713</v>
       </c>
     </row>
@@ -15947,6 +16557,12 @@
         <v>-0.7789098904792293</v>
       </c>
       <c r="D102" t="n">
+        <v>-0.5254200011778133</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.2534898893014161</v>
+      </c>
+      <c r="F102" t="n">
         <v>0.7789098904792293</v>
       </c>
     </row>
@@ -15965,6 +16581,12 @@
         <v>-0.7745491628333183</v>
       </c>
       <c r="D103" t="n">
+        <v>-0.8193153109369031</v>
+      </c>
+      <c r="E103" t="n">
+        <v>-0.04476614810358482</v>
+      </c>
+      <c r="F103" t="n">
         <v>0.7745491628333183</v>
       </c>
     </row>
@@ -15983,6 +16605,12 @@
         <v>0.7709354153535717</v>
       </c>
       <c r="D104" t="n">
+        <v>-0.2985945042354343</v>
+      </c>
+      <c r="E104" t="n">
+        <v>-1.069529919589006</v>
+      </c>
+      <c r="F104" t="n">
         <v>0.7709354153535717</v>
       </c>
     </row>
@@ -16001,6 +16629,12 @@
         <v>-0.7658962043790394</v>
       </c>
       <c r="D105" t="n">
+        <v>1.433964888602058</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2.199861092981097</v>
+      </c>
+      <c r="F105" t="n">
         <v>0.7658962043790394</v>
       </c>
     </row>
@@ -16019,6 +16653,12 @@
         <v>-0.7625580839446719</v>
       </c>
       <c r="D106" t="n">
+        <v>-0.1610539625223787</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.6015041214222933</v>
+      </c>
+      <c r="F106" t="n">
         <v>0.7625580839446719</v>
       </c>
     </row>
@@ -16037,6 +16677,12 @@
         <v>0.7619484397429417</v>
       </c>
       <c r="D107" t="n">
+        <v>1.825378770768807</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1.063430331025865</v>
+      </c>
+      <c r="F107" t="n">
         <v>0.7619484397429417</v>
       </c>
     </row>
@@ -16055,6 +16701,12 @@
         <v>-0.7611002680348764</v>
       </c>
       <c r="D108" t="n">
+        <v>-0.6091673965784307</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.1519328714564457</v>
+      </c>
+      <c r="F108" t="n">
         <v>0.7611002680348764</v>
       </c>
     </row>
@@ -16073,6 +16725,12 @@
         <v>-0.7574249531569848</v>
       </c>
       <c r="D109" t="n">
+        <v>9.660028485891658</v>
+      </c>
+      <c r="E109" t="n">
+        <v>10.41745343904864</v>
+      </c>
+      <c r="F109" t="n">
         <v>0.7574249531569848</v>
       </c>
     </row>
@@ -16091,6 +16749,12 @@
         <v>0.7297582804487243</v>
       </c>
       <c r="D110" t="n">
+        <v>0.1398282153807149</v>
+      </c>
+      <c r="E110" t="n">
+        <v>-0.5899300650680094</v>
+      </c>
+      <c r="F110" t="n">
         <v>0.7297582804487243</v>
       </c>
     </row>
@@ -16109,6 +16773,12 @@
         <v>0.7232741256813936</v>
       </c>
       <c r="D111" t="n">
+        <v>-0.1339018409983303</v>
+      </c>
+      <c r="E111" t="n">
+        <v>-0.857175966679724</v>
+      </c>
+      <c r="F111" t="n">
         <v>0.7232741256813936</v>
       </c>
     </row>
@@ -16127,6 +16797,12 @@
         <v>0.7218012536880404</v>
       </c>
       <c r="D112" t="n">
+        <v>0.5679032674377212</v>
+      </c>
+      <c r="E112" t="n">
+        <v>-0.1538979862503191</v>
+      </c>
+      <c r="F112" t="n">
         <v>0.7218012536880404</v>
       </c>
     </row>
@@ -16145,6 +16821,12 @@
         <v>-0.7143060283701403</v>
       </c>
       <c r="D113" t="n">
+        <v>0.3498132906715075</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1.064119319041648</v>
+      </c>
+      <c r="F113" t="n">
         <v>0.7143060283701403</v>
       </c>
     </row>
@@ -16163,6 +16845,12 @@
         <v>0.7068129008069172</v>
       </c>
       <c r="D114" t="n">
+        <v>0.6063383497204881</v>
+      </c>
+      <c r="E114" t="n">
+        <v>-0.1004745510864291</v>
+      </c>
+      <c r="F114" t="n">
         <v>0.7068129008069172</v>
       </c>
     </row>
@@ -16181,6 +16869,12 @@
         <v>-0.6846841362271515</v>
       </c>
       <c r="D115" t="n">
+        <v>0.1989603128835844</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.8836444491107359</v>
+      </c>
+      <c r="F115" t="n">
         <v>0.6846841362271515</v>
       </c>
     </row>
@@ -16199,6 +16893,12 @@
         <v>-0.6834563615156454</v>
       </c>
       <c r="D116" t="n">
+        <v>-0.5721539955349234</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.1113023659807219</v>
+      </c>
+      <c r="F116" t="n">
         <v>0.6834563615156454</v>
       </c>
     </row>
@@ -16217,6 +16917,12 @@
         <v>-0.6824788630978448</v>
       </c>
       <c r="D117" t="n">
+        <v>0.06489563614385709</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.7473744992417019</v>
+      </c>
+      <c r="F117" t="n">
         <v>0.6824788630978448</v>
       </c>
     </row>
@@ -16235,6 +16941,12 @@
         <v>-0.6783105824400304</v>
       </c>
       <c r="D118" t="n">
+        <v>-0.4320456256991858</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.2462649567408446</v>
+      </c>
+      <c r="F118" t="n">
         <v>0.6783105824400304</v>
       </c>
     </row>
@@ -16253,6 +16965,12 @@
         <v>0.676215455008893</v>
       </c>
       <c r="D119" t="n">
+        <v>0.7373544186700667</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.06113896366117361</v>
+      </c>
+      <c r="F119" t="n">
         <v>0.676215455008893</v>
       </c>
     </row>
@@ -16271,6 +16989,12 @@
         <v>-0.6752587520418164</v>
       </c>
       <c r="D120" t="n">
+        <v>-0.5357585517415101</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.1395002003003063</v>
+      </c>
+      <c r="F120" t="n">
         <v>0.6752587520418164</v>
       </c>
     </row>
@@ -16289,6 +17013,12 @@
         <v>-0.6725343570015202</v>
       </c>
       <c r="D121" t="n">
+        <v>-0.3302584512070151</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.3422759057945051</v>
+      </c>
+      <c r="F121" t="n">
         <v>0.6725343570015202</v>
       </c>
     </row>
@@ -16307,6 +17037,12 @@
         <v>0.665224185092876</v>
       </c>
       <c r="D122" t="n">
+        <v>2.121656085174158</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.456431900081282</v>
+      </c>
+      <c r="F122" t="n">
         <v>0.665224185092876</v>
       </c>
     </row>
@@ -16325,6 +17061,12 @@
         <v>0.6642023588364685</v>
       </c>
       <c r="D123" t="n">
+        <v>0.6927418053468904</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.02853944651042194</v>
+      </c>
+      <c r="F123" t="n">
         <v>0.6642023588364685</v>
       </c>
     </row>
@@ -16343,6 +17085,12 @@
         <v>0.6638867693928602</v>
       </c>
       <c r="D124" t="n">
+        <v>0.6915555554467958</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.02766878605393569</v>
+      </c>
+      <c r="F124" t="n">
         <v>0.6638867693928602</v>
       </c>
     </row>
@@ -16361,6 +17109,12 @@
         <v>0.6624275240724442</v>
       </c>
       <c r="D125" t="n">
+        <v>0.5295617201595646</v>
+      </c>
+      <c r="E125" t="n">
+        <v>-0.1328658039128796</v>
+      </c>
+      <c r="F125" t="n">
         <v>0.6624275240724442</v>
       </c>
     </row>
@@ -16379,6 +17133,12 @@
         <v>-0.6579962936383805</v>
       </c>
       <c r="D126" t="n">
+        <v>2.655330974741047</v>
+      </c>
+      <c r="E126" t="n">
+        <v>3.313327268379428</v>
+      </c>
+      <c r="F126" t="n">
         <v>0.6579962936383805</v>
       </c>
     </row>
@@ -16397,6 +17157,12 @@
         <v>0.6547851049561842</v>
       </c>
       <c r="D127" t="n">
+        <v>0.5838969844553505</v>
+      </c>
+      <c r="E127" t="n">
+        <v>-0.07088812050083372</v>
+      </c>
+      <c r="F127" t="n">
         <v>0.6547851049561842</v>
       </c>
     </row>
@@ -16415,6 +17181,12 @@
         <v>-0.6546253045840855</v>
       </c>
       <c r="D128" t="n">
+        <v>0.4178425063327034</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1.072467810916789</v>
+      </c>
+      <c r="F128" t="n">
         <v>0.6546253045840855</v>
       </c>
     </row>
@@ -16433,6 +17205,12 @@
         <v>-0.6513477509930103</v>
       </c>
       <c r="D129" t="n">
+        <v>-0.7276285702275419</v>
+      </c>
+      <c r="E129" t="n">
+        <v>-0.0762808192345316</v>
+      </c>
+      <c r="F129" t="n">
         <v>0.6513477509930103</v>
       </c>
     </row>
@@ -16451,6 +17229,12 @@
         <v>0.6472551338176846</v>
       </c>
       <c r="D130" t="n">
+        <v>0.159298130624982</v>
+      </c>
+      <c r="E130" t="n">
+        <v>-0.4879570031927027</v>
+      </c>
+      <c r="F130" t="n">
         <v>0.6472551338176846</v>
       </c>
     </row>
@@ -16469,6 +17253,12 @@
         <v>0.6028208672958477</v>
       </c>
       <c r="D131" t="n">
+        <v>-0.7669871477533616</v>
+      </c>
+      <c r="E131" t="n">
+        <v>-1.369808015049209</v>
+      </c>
+      <c r="F131" t="n">
         <v>0.6028208672958477</v>
       </c>
     </row>
@@ -16487,6 +17277,12 @@
         <v>0.6018089258153314</v>
       </c>
       <c r="D132" t="n">
+        <v>0.5213136124773313</v>
+      </c>
+      <c r="E132" t="n">
+        <v>-0.08049531333800003</v>
+      </c>
+      <c r="F132" t="n">
         <v>0.6018089258153314</v>
       </c>
     </row>
@@ -16505,6 +17301,12 @@
         <v>0.599724125055705</v>
       </c>
       <c r="D133" t="n">
+        <v>3.631018115029931</v>
+      </c>
+      <c r="E133" t="n">
+        <v>3.031293989974226</v>
+      </c>
+      <c r="F133" t="n">
         <v>0.599724125055705</v>
       </c>
     </row>
@@ -16523,6 +17325,12 @@
         <v>-0.5944135770956784</v>
       </c>
       <c r="D134" t="n">
+        <v>-0.1144233032718417</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4799902738238367</v>
+      </c>
+      <c r="F134" t="n">
         <v>0.5944135770956784</v>
       </c>
     </row>
@@ -16541,6 +17349,12 @@
         <v>0.5931274350793959</v>
       </c>
       <c r="D135" t="n">
+        <v>-0.0632860432429051</v>
+      </c>
+      <c r="E135" t="n">
+        <v>-0.656413478322301</v>
+      </c>
+      <c r="F135" t="n">
         <v>0.5931274350793959</v>
       </c>
     </row>
@@ -16559,6 +17373,12 @@
         <v>-0.5885774124824154</v>
       </c>
       <c r="D136" t="n">
+        <v>-0.5010685792490014</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.08750883323341396</v>
+      </c>
+      <c r="F136" t="n">
         <v>0.5885774124824154</v>
       </c>
     </row>
@@ -16577,6 +17397,12 @@
         <v>0.5843916959924407</v>
       </c>
       <c r="D137" t="n">
+        <v>-0.1838816100829843</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.768273306075425</v>
+      </c>
+      <c r="F137" t="n">
         <v>0.5843916959924407</v>
       </c>
     </row>
@@ -16595,6 +17421,12 @@
         <v>-0.5761363365310022</v>
       </c>
       <c r="D138" t="n">
+        <v>-1.260574388501108</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.6844380519701057</v>
+      </c>
+      <c r="F138" t="n">
         <v>0.5761363365310022</v>
       </c>
     </row>
@@ -16613,6 +17445,12 @@
         <v>-0.5723921253269737</v>
       </c>
       <c r="D139" t="n">
+        <v>-0.5293620070144399</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.04303011831253382</v>
+      </c>
+      <c r="F139" t="n">
         <v>0.5723921253269737</v>
       </c>
     </row>
@@ -16631,6 +17469,12 @@
         <v>0.570292271698134</v>
       </c>
       <c r="D140" t="n">
+        <v>0.2607429091323802</v>
+      </c>
+      <c r="E140" t="n">
+        <v>-0.3095493625657538</v>
+      </c>
+      <c r="F140" t="n">
         <v>0.570292271698134</v>
       </c>
     </row>
@@ -16649,6 +17493,12 @@
         <v>-0.5678342708127812</v>
       </c>
       <c r="D141" t="n">
+        <v>-0.186931199668675</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3809030711441062</v>
+      </c>
+      <c r="F141" t="n">
         <v>0.5678342708127812</v>
       </c>
     </row>
@@ -16667,6 +17517,12 @@
         <v>0.5658021009492815</v>
       </c>
       <c r="D142" t="n">
+        <v>0.2521673827294391</v>
+      </c>
+      <c r="E142" t="n">
+        <v>-0.3136347182198424</v>
+      </c>
+      <c r="F142" t="n">
         <v>0.5658021009492815</v>
       </c>
     </row>
@@ -16685,6 +17541,12 @@
         <v>-0.5624753413047623</v>
       </c>
       <c r="D143" t="n">
+        <v>4.595447856433638</v>
+      </c>
+      <c r="E143" t="n">
+        <v>5.1579231977384</v>
+      </c>
+      <c r="F143" t="n">
         <v>0.5624753413047623</v>
       </c>
     </row>
@@ -16703,6 +17565,12 @@
         <v>-0.5562568477057369</v>
       </c>
       <c r="D144" t="n">
+        <v>-0.6271449682065707</v>
+      </c>
+      <c r="E144" t="n">
+        <v>-0.07088812050083383</v>
+      </c>
+      <c r="F144" t="n">
         <v>0.5562568477057369</v>
       </c>
     </row>
@@ -16721,6 +17589,12 @@
         <v>0.54951530562254</v>
       </c>
       <c r="D145" t="n">
+        <v>-0.2135760008480116</v>
+      </c>
+      <c r="E145" t="n">
+        <v>-0.7630913064705517</v>
+      </c>
+      <c r="F145" t="n">
         <v>0.54951530562254</v>
       </c>
     </row>
@@ -16739,6 +17613,12 @@
         <v>-0.542367963780748</v>
       </c>
       <c r="D146" t="n">
+        <v>0.290833164518843</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.833201128299591</v>
+      </c>
+      <c r="F146" t="n">
         <v>0.542367963780748</v>
       </c>
     </row>
@@ -16757,6 +17637,12 @@
         <v>0.5397337369965614</v>
       </c>
       <c r="D147" t="n">
+        <v>-0.4628883979510078</v>
+      </c>
+      <c r="E147" t="n">
+        <v>-1.002622134947569</v>
+      </c>
+      <c r="F147" t="n">
         <v>0.5397337369965614</v>
       </c>
     </row>
@@ -16775,6 +17661,12 @@
         <v>0.5378921458277985</v>
       </c>
       <c r="D148" t="n">
+        <v>3.190497816086409</v>
+      </c>
+      <c r="E148" t="n">
+        <v>2.652605670258611</v>
+      </c>
+      <c r="F148" t="n">
         <v>0.5378921458277985</v>
       </c>
     </row>
@@ -16793,6 +17685,12 @@
         <v>0.5366797576576182</v>
       </c>
       <c r="D149" t="n">
+        <v>0.2913599040435569</v>
+      </c>
+      <c r="E149" t="n">
+        <v>-0.2453198536140613</v>
+      </c>
+      <c r="F149" t="n">
         <v>0.5366797576576182</v>
       </c>
     </row>
@@ -16811,6 +17709,12 @@
         <v>0.532085704831907</v>
       </c>
       <c r="D150" t="n">
+        <v>-0.007018558208575544</v>
+      </c>
+      <c r="E150" t="n">
+        <v>-0.5391042630404825</v>
+      </c>
+      <c r="F150" t="n">
         <v>0.532085704831907</v>
       </c>
     </row>
@@ -16829,6 +17733,12 @@
         <v>-0.5260600013806466</v>
       </c>
       <c r="D151" t="n">
+        <v>-0.4802776092487678</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.04578239213187877</v>
+      </c>
+      <c r="F151" t="n">
         <v>0.5260600013806466</v>
       </c>
     </row>
@@ -16847,6 +17757,12 @@
         <v>0.5226747435592388</v>
       </c>
       <c r="D152" t="n">
+        <v>-0.146901070539097</v>
+      </c>
+      <c r="E152" t="n">
+        <v>-0.6695758140983358</v>
+      </c>
+      <c r="F152" t="n">
         <v>0.5226747435592388</v>
       </c>
     </row>
@@ -16865,6 +17781,12 @@
         <v>-0.5222840200472155</v>
       </c>
       <c r="D153" t="n">
+        <v>0.5702103095129553</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1.092494329560171</v>
+      </c>
+      <c r="F153" t="n">
         <v>0.5222840200472155</v>
       </c>
     </row>
@@ -16883,6 +17805,12 @@
         <v>0.5157710631566286</v>
       </c>
       <c r="D154" t="n">
+        <v>-0.04855960533897966</v>
+      </c>
+      <c r="E154" t="n">
+        <v>-0.5643306684956082</v>
+      </c>
+      <c r="F154" t="n">
         <v>0.5157710631566286</v>
       </c>
     </row>
@@ -16901,6 +17829,12 @@
         <v>-0.5121490507736322</v>
       </c>
       <c r="D155" t="n">
+        <v>1.043933354205548</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1.55608240497918</v>
+      </c>
+      <c r="F155" t="n">
         <v>0.5121490507736322</v>
       </c>
     </row>
@@ -16919,6 +17853,12 @@
         <v>-0.5074692743706195</v>
       </c>
       <c r="D156" t="n">
+        <v>-0.1154394942095969</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.3920297801610227</v>
+      </c>
+      <c r="F156" t="n">
         <v>0.5074692743706195</v>
       </c>
     </row>
@@ -16937,6 +17877,12 @@
         <v>-0.5055944224621425</v>
       </c>
       <c r="D157" t="n">
+        <v>-0.8093399593294019</v>
+      </c>
+      <c r="E157" t="n">
+        <v>-0.3037455368672595</v>
+      </c>
+      <c r="F157" t="n">
         <v>0.5055944224621425</v>
       </c>
     </row>
@@ -16955,6 +17901,12 @@
         <v>0.4935353135318855</v>
       </c>
       <c r="D158" t="n">
+        <v>0.5158624142638819</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.02232710073199639</v>
+      </c>
+      <c r="F158" t="n">
         <v>0.4935353135318855</v>
       </c>
     </row>
@@ -16973,6 +17925,12 @@
         <v>0.4885216509050959</v>
       </c>
       <c r="D159" t="n">
+        <v>0.8371425953940025</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.3486209444889066</v>
+      </c>
+      <c r="F159" t="n">
         <v>0.4885216509050959</v>
       </c>
     </row>
@@ -16991,6 +17949,12 @@
         <v>0.4873177349588331</v>
       </c>
       <c r="D160" t="n">
+        <v>0.5168024762487399</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.02948474128990681</v>
+      </c>
+      <c r="F160" t="n">
         <v>0.4873177349588331</v>
       </c>
     </row>
@@ -17009,6 +17973,12 @@
         <v>0.4853375970925801</v>
       </c>
       <c r="D161" t="n">
+        <v>-0.9309695827162093</v>
+      </c>
+      <c r="E161" t="n">
+        <v>-1.416307179808789</v>
+      </c>
+      <c r="F161" t="n">
         <v>0.4853375970925801</v>
       </c>
     </row>
@@ -17027,6 +17997,12 @@
         <v>-0.482392878890116</v>
       </c>
       <c r="D162" t="n">
+        <v>0.1819693831626984</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.6643622620528143</v>
+      </c>
+      <c r="F162" t="n">
         <v>0.482392878890116</v>
       </c>
     </row>
@@ -17045,6 +18021,12 @@
         <v>-0.4821129412876828</v>
       </c>
       <c r="D163" t="n">
+        <v>-0.8001604539493042</v>
+      </c>
+      <c r="E163" t="n">
+        <v>-0.3180475126616215</v>
+      </c>
+      <c r="F163" t="n">
         <v>0.4821129412876828</v>
       </c>
     </row>
@@ -17063,6 +18045,12 @@
         <v>-0.4820421245421418</v>
       </c>
       <c r="D164" t="n">
+        <v>-0.5285835944746853</v>
+      </c>
+      <c r="E164" t="n">
+        <v>-0.04654146993254343</v>
+      </c>
+      <c r="F164" t="n">
         <v>0.4820421245421418</v>
       </c>
     </row>
@@ -17081,6 +18069,12 @@
         <v>-0.4817373885151319</v>
       </c>
       <c r="D165" t="n">
+        <v>0.1495756727149396</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.6313130612300715</v>
+      </c>
+      <c r="F165" t="n">
         <v>0.4817373885151319</v>
       </c>
     </row>
@@ -17099,6 +18093,12 @@
         <v>-0.4790787676492003</v>
       </c>
       <c r="D166" t="n">
+        <v>-1.600128454529629</v>
+      </c>
+      <c r="E166" t="n">
+        <v>-1.121049686880429</v>
+      </c>
+      <c r="F166" t="n">
         <v>0.4790787676492003</v>
       </c>
     </row>
@@ -17117,6 +18117,12 @@
         <v>0.4649057686390368</v>
       </c>
       <c r="D167" t="n">
+        <v>0.130940138696177</v>
+      </c>
+      <c r="E167" t="n">
+        <v>-0.3339656299428598</v>
+      </c>
+      <c r="F167" t="n">
         <v>0.4649057686390368</v>
       </c>
     </row>
@@ -17135,6 +18141,12 @@
         <v>-0.4645548353575119</v>
       </c>
       <c r="D168" t="n">
+        <v>-0.976759202147829</v>
+      </c>
+      <c r="E168" t="n">
+        <v>-0.5122043667903171</v>
+      </c>
+      <c r="F168" t="n">
         <v>0.4645548353575119</v>
       </c>
     </row>
@@ -17153,6 +18165,12 @@
         <v>-0.4641433844707529</v>
       </c>
       <c r="D169" t="n">
+        <v>0.4765686727570015</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.9407120572277544</v>
+      </c>
+      <c r="F169" t="n">
         <v>0.4641433844707529</v>
       </c>
     </row>
@@ -17171,6 +18189,12 @@
         <v>-0.4641283618312096</v>
       </c>
       <c r="D170" t="n">
+        <v>0.007110184477881997</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.4712385463090916</v>
+      </c>
+      <c r="F170" t="n">
         <v>0.4641283618312096</v>
       </c>
     </row>
@@ -17189,6 +18213,12 @@
         <v>-0.4609559341081902</v>
       </c>
       <c r="D171" t="n">
+        <v>-0.8448724248054239</v>
+      </c>
+      <c r="E171" t="n">
+        <v>-0.3839164906972337</v>
+      </c>
+      <c r="F171" t="n">
         <v>0.4609559341081902</v>
       </c>
     </row>
@@ -17207,6 +18237,12 @@
         <v>-0.459638657083148</v>
       </c>
       <c r="D172" t="n">
+        <v>-0.3009583222707073</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.1586803348124407</v>
+      </c>
+      <c r="F172" t="n">
         <v>0.459638657083148</v>
       </c>
     </row>
@@ -17225,6 +18261,12 @@
         <v>0.4570815589789793</v>
       </c>
       <c r="D173" t="n">
+        <v>0.08204540321413838</v>
+      </c>
+      <c r="E173" t="n">
+        <v>-0.3750361557648409</v>
+      </c>
+      <c r="F173" t="n">
         <v>0.4570815589789793</v>
       </c>
     </row>
@@ -17243,6 +18285,12 @@
         <v>-0.4517367195695329</v>
       </c>
       <c r="D174" t="n">
+        <v>-0.8665119288465182</v>
+      </c>
+      <c r="E174" t="n">
+        <v>-0.4147752092769853</v>
+      </c>
+      <c r="F174" t="n">
         <v>0.4517367195695329</v>
       </c>
     </row>
@@ -17261,6 +18309,12 @@
         <v>-0.451117650961581</v>
       </c>
       <c r="D175" t="n">
+        <v>-0.3396982631094513</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.1114193878521296</v>
+      </c>
+      <c r="F175" t="n">
         <v>0.451117650961581</v>
       </c>
     </row>
@@ -17279,6 +18333,12 @@
         <v>0.4486547356257912</v>
       </c>
       <c r="D176" t="n">
+        <v>-0.1979021820748835</v>
+      </c>
+      <c r="E176" t="n">
+        <v>-0.6465569177006747</v>
+      </c>
+      <c r="F176" t="n">
         <v>0.4486547356257912</v>
       </c>
     </row>
@@ -17297,6 +18357,12 @@
         <v>-0.4473805788404623</v>
       </c>
       <c r="D177" t="n">
+        <v>0.01572812008183259</v>
+      </c>
+      <c r="E177" t="n">
+        <v>0.4631086989222949</v>
+      </c>
+      <c r="F177" t="n">
         <v>0.4473805788404623</v>
       </c>
     </row>
@@ -17315,6 +18381,12 @@
         <v>0.4423164274591352</v>
       </c>
       <c r="D178" t="n">
+        <v>0.1979019973367644</v>
+      </c>
+      <c r="E178" t="n">
+        <v>-0.2444144301223709</v>
+      </c>
+      <c r="F178" t="n">
         <v>0.4423164274591352</v>
       </c>
     </row>
@@ -17333,6 +18405,12 @@
         <v>-0.4342689391479085</v>
       </c>
       <c r="D179" t="n">
+        <v>0.01107783274252279</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0.4453467718904313</v>
+      </c>
+      <c r="F179" t="n">
         <v>0.4342689391479085</v>
       </c>
     </row>
@@ -17351,6 +18429,12 @@
         <v>0.4304443456592445</v>
       </c>
       <c r="D180" t="n">
+        <v>-0.969606004846869</v>
+      </c>
+      <c r="E180" t="n">
+        <v>-1.400050350506113</v>
+      </c>
+      <c r="F180" t="n">
         <v>0.4304443456592445</v>
       </c>
     </row>
@@ -17369,6 +18453,12 @@
         <v>0.4260440535607078</v>
       </c>
       <c r="D181" t="n">
+        <v>0.005955329253490306</v>
+      </c>
+      <c r="E181" t="n">
+        <v>-0.4200887243072176</v>
+      </c>
+      <c r="F181" t="n">
         <v>0.4260440535607078</v>
       </c>
     </row>
@@ -17387,6 +18477,12 @@
         <v>-0.4234067730612064</v>
       </c>
       <c r="D182" t="n">
+        <v>-0.2799670979589958</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.1434396751022107</v>
+      </c>
+      <c r="F182" t="n">
         <v>0.4234067730612064</v>
       </c>
     </row>
@@ -17405,6 +18501,12 @@
         <v>0.4214760961335901</v>
       </c>
       <c r="D183" t="n">
+        <v>0.1324330539356843</v>
+      </c>
+      <c r="E183" t="n">
+        <v>-0.2890430421979058</v>
+      </c>
+      <c r="F183" t="n">
         <v>0.4214760961335901</v>
       </c>
     </row>
@@ -17423,6 +18525,12 @@
         <v>0.418030042673142</v>
       </c>
       <c r="D184" t="n">
+        <v>-0.3023345631224975</v>
+      </c>
+      <c r="E184" t="n">
+        <v>-0.7203646057956395</v>
+      </c>
+      <c r="F184" t="n">
         <v>0.418030042673142</v>
       </c>
     </row>
@@ -17441,6 +18549,12 @@
         <v>-0.4163182666620014</v>
       </c>
       <c r="D185" t="n">
+        <v>-0.9335179026869597</v>
+      </c>
+      <c r="E185" t="n">
+        <v>-0.5171996360249582</v>
+      </c>
+      <c r="F185" t="n">
         <v>0.4163182666620014</v>
       </c>
     </row>
@@ -17459,6 +18573,12 @@
         <v>0.411241188807879</v>
       </c>
       <c r="D186" t="n">
+        <v>0.7719997250127899</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0.3607585362049109</v>
+      </c>
+      <c r="F186" t="n">
         <v>0.411241188807879</v>
       </c>
     </row>
@@ -17477,6 +18597,12 @@
         <v>-0.4082102192486823</v>
       </c>
       <c r="D187" t="n">
+        <v>-0.4248030834094731</v>
+      </c>
+      <c r="E187" t="n">
+        <v>-0.01659286416079079</v>
+      </c>
+      <c r="F187" t="n">
         <v>0.4082102192486823</v>
       </c>
     </row>
@@ -17495,6 +18621,12 @@
         <v>0.4067146458460622</v>
       </c>
       <c r="D188" t="n">
+        <v>0.6625962899400262</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0.255881644093964</v>
+      </c>
+      <c r="F188" t="n">
         <v>0.4067146458460622</v>
       </c>
     </row>
@@ -17513,6 +18645,12 @@
         <v>0.4053187422212997</v>
       </c>
       <c r="D189" t="n">
+        <v>0.265841975268568</v>
+      </c>
+      <c r="E189" t="n">
+        <v>-0.1394767669527317</v>
+      </c>
+      <c r="F189" t="n">
         <v>0.4053187422212997</v>
       </c>
     </row>
@@ -17531,6 +18669,12 @@
         <v>0.4032083886686008</v>
       </c>
       <c r="D190" t="n">
+        <v>0.2822483371702877</v>
+      </c>
+      <c r="E190" t="n">
+        <v>-0.1209600514983131</v>
+      </c>
+      <c r="F190" t="n">
         <v>0.4032083886686008</v>
       </c>
     </row>
@@ -17549,6 +18693,12 @@
         <v>-0.4008324255113351</v>
       </c>
       <c r="D191" t="n">
+        <v>-0.2233437924365056</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.1774886330748295</v>
+      </c>
+      <c r="F191" t="n">
         <v>0.4008324255113351</v>
       </c>
     </row>
@@ -17567,6 +18717,12 @@
         <v>-0.3992357663313386</v>
       </c>
       <c r="D192" t="n">
+        <v>0.3638330559014634</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0.763068822232802</v>
+      </c>
+      <c r="F192" t="n">
         <v>0.3992357663313386</v>
       </c>
     </row>
@@ -17585,6 +18741,12 @@
         <v>-0.3900493932450885</v>
       </c>
       <c r="D193" t="n">
+        <v>-0.5162924551362252</v>
+      </c>
+      <c r="E193" t="n">
+        <v>-0.1262430618911368</v>
+      </c>
+      <c r="F193" t="n">
         <v>0.3900493932450885</v>
       </c>
     </row>
@@ -17603,6 +18765,12 @@
         <v>0.3888349011871748</v>
       </c>
       <c r="D194" t="n">
+        <v>5.285121591208622</v>
+      </c>
+      <c r="E194" t="n">
+        <v>4.896286690021447</v>
+      </c>
+      <c r="F194" t="n">
         <v>0.3888349011871748</v>
       </c>
     </row>
@@ -17621,6 +18789,12 @@
         <v>0.379073593296505</v>
       </c>
       <c r="D195" t="n">
+        <v>0.09194156926729657</v>
+      </c>
+      <c r="E195" t="n">
+        <v>-0.2871320240292085</v>
+      </c>
+      <c r="F195" t="n">
         <v>0.379073593296505</v>
       </c>
     </row>
@@ -17639,6 +18813,12 @@
         <v>-0.3725982732025455</v>
       </c>
       <c r="D196" t="n">
+        <v>-0.5406788259145292</v>
+      </c>
+      <c r="E196" t="n">
+        <v>-0.1680805527119837</v>
+      </c>
+      <c r="F196" t="n">
         <v>0.3725982732025455</v>
       </c>
     </row>
@@ -17657,6 +18837,12 @@
         <v>0.3709797739003498</v>
       </c>
       <c r="D197" t="n">
+        <v>0.7157909309528937</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0.3448111570525439</v>
+      </c>
+      <c r="F197" t="n">
         <v>0.3709797739003498</v>
       </c>
     </row>
@@ -17675,6 +18861,12 @@
         <v>0.3641154823977733</v>
       </c>
       <c r="D198" t="n">
+        <v>0.2488026150698408</v>
+      </c>
+      <c r="E198" t="n">
+        <v>-0.1153128673279325</v>
+      </c>
+      <c r="F198" t="n">
         <v>0.3641154823977733</v>
       </c>
     </row>
@@ -17693,6 +18885,12 @@
         <v>0.3618623174119466</v>
       </c>
       <c r="D199" t="n">
+        <v>-0.2788078115690354</v>
+      </c>
+      <c r="E199" t="n">
+        <v>-0.6406701289809821</v>
+      </c>
+      <c r="F199" t="n">
         <v>0.3618623174119466</v>
       </c>
     </row>
@@ -17711,6 +18909,12 @@
         <v>0.3583924593552528</v>
       </c>
       <c r="D200" t="n">
+        <v>0.2086009961585387</v>
+      </c>
+      <c r="E200" t="n">
+        <v>-0.149791463196714</v>
+      </c>
+      <c r="F200" t="n">
         <v>0.3583924593552528</v>
       </c>
     </row>
@@ -17729,6 +18933,12 @@
         <v>-0.35819570141984</v>
       </c>
       <c r="D201" t="n">
+        <v>0.0223410343535169</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0.3805367357733569</v>
+      </c>
+      <c r="F201" t="n">
         <v>0.35819570141984</v>
       </c>
     </row>
@@ -17747,6 +18957,12 @@
         <v>0.350924232722138</v>
       </c>
       <c r="D202" t="n">
+        <v>-0.2328168729268655</v>
+      </c>
+      <c r="E202" t="n">
+        <v>-0.5837411056490035</v>
+      </c>
+      <c r="F202" t="n">
         <v>0.350924232722138</v>
       </c>
     </row>
@@ -17765,6 +18981,12 @@
         <v>0.3492154360355268</v>
       </c>
       <c r="D203" t="n">
+        <v>13.18639370366975</v>
+      </c>
+      <c r="E203" t="n">
+        <v>12.83717826763422</v>
+      </c>
+      <c r="F203" t="n">
         <v>0.3492154360355268</v>
       </c>
     </row>
@@ -17783,6 +19005,12 @@
         <v>0.3482021816385244</v>
       </c>
       <c r="D204" t="n">
+        <v>0.05595431177150407</v>
+      </c>
+      <c r="E204" t="n">
+        <v>-0.2922478698670203</v>
+      </c>
+      <c r="F204" t="n">
         <v>0.3482021816385244</v>
       </c>
     </row>
@@ -17801,6 +19029,12 @@
         <v>0.3477099154857238</v>
       </c>
       <c r="D205" t="n">
+        <v>0.7570507955234931</v>
+      </c>
+      <c r="E205" t="n">
+        <v>0.4093408800377693</v>
+      </c>
+      <c r="F205" t="n">
         <v>0.3477099154857238</v>
       </c>
     </row>
@@ -17819,6 +19053,12 @@
         <v>-0.3455427579366691</v>
       </c>
       <c r="D206" t="n">
+        <v>0.05432112316310442</v>
+      </c>
+      <c r="E206" t="n">
+        <v>0.3998638810997736</v>
+      </c>
+      <c r="F206" t="n">
         <v>0.3455427579366691</v>
       </c>
     </row>
@@ -17837,6 +19077,12 @@
         <v>0.3418649961361881</v>
       </c>
       <c r="D207" t="n">
+        <v>0.2590210625581749</v>
+      </c>
+      <c r="E207" t="n">
+        <v>-0.08284393357801327</v>
+      </c>
+      <c r="F207" t="n">
         <v>0.3418649961361881</v>
       </c>
     </row>
@@ -17855,6 +19101,12 @@
         <v>-0.3407511698619085</v>
       </c>
       <c r="D208" t="n">
+        <v>-0.4054656761116524</v>
+      </c>
+      <c r="E208" t="n">
+        <v>-0.06471450624974391</v>
+      </c>
+      <c r="F208" t="n">
         <v>0.3407511698619085</v>
       </c>
     </row>
@@ -17873,6 +19125,12 @@
         <v>-0.3378410859524704</v>
       </c>
       <c r="D209" t="n">
+        <v>-0.6137828267761434</v>
+      </c>
+      <c r="E209" t="n">
+        <v>-0.275941740823673</v>
+      </c>
+      <c r="F209" t="n">
         <v>0.3378410859524704</v>
       </c>
     </row>
@@ -17891,6 +19149,12 @@
         <v>0.3366959596642084</v>
       </c>
       <c r="D210" t="n">
+        <v>0.7420428787834337</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0.4053469191192253</v>
+      </c>
+      <c r="F210" t="n">
         <v>0.3366959596642084</v>
       </c>
     </row>
@@ -17909,6 +19173,12 @@
         <v>0.3352710889604531</v>
       </c>
       <c r="D211" t="n">
+        <v>0.3497765555105479</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0.01450546655009474</v>
+      </c>
+      <c r="F211" t="n">
         <v>0.3352710889604531</v>
       </c>
     </row>
@@ -17927,6 +19197,12 @@
         <v>0.3318717317384172</v>
       </c>
       <c r="D212" t="n">
+        <v>0.5149824275366948</v>
+      </c>
+      <c r="E212" t="n">
+        <v>0.1831106957982775</v>
+      </c>
+      <c r="F212" t="n">
         <v>0.3318717317384172</v>
       </c>
     </row>
@@ -17945,6 +19221,12 @@
         <v>0.3285262610377355</v>
       </c>
       <c r="D213" t="n">
+        <v>0.04496450111792307</v>
+      </c>
+      <c r="E213" t="n">
+        <v>-0.2835617599198125</v>
+      </c>
+      <c r="F213" t="n">
         <v>0.3285262610377355</v>
       </c>
     </row>
@@ -17963,6 +19245,12 @@
         <v>-0.3198111659283044</v>
       </c>
       <c r="D214" t="n">
+        <v>-0.3298886719767246</v>
+      </c>
+      <c r="E214" t="n">
+        <v>-0.01007750604842011</v>
+      </c>
+      <c r="F214" t="n">
         <v>0.3198111659283044</v>
       </c>
     </row>
@@ -17981,6 +19269,12 @@
         <v>-0.3193550413204206</v>
       </c>
       <c r="D215" t="n">
+        <v>0.05988322622077741</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0.379238267541198</v>
+      </c>
+      <c r="F215" t="n">
         <v>0.3193550413204206</v>
       </c>
     </row>
@@ -17999,6 +19293,12 @@
         <v>-0.3162007097771712</v>
       </c>
       <c r="D216" t="n">
+        <v>-0.03445798520958528</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0.281742724567586</v>
+      </c>
+      <c r="F216" t="n">
         <v>0.3162007097771712</v>
       </c>
     </row>
@@ -18017,6 +19317,12 @@
         <v>-0.3153477535315809</v>
       </c>
       <c r="D217" t="n">
+        <v>-0.343384686824962</v>
+      </c>
+      <c r="E217" t="n">
+        <v>-0.02803693329338109</v>
+      </c>
+      <c r="F217" t="n">
         <v>0.3153477535315809</v>
       </c>
     </row>
@@ -18035,6 +19341,12 @@
         <v>-0.3101398145647133</v>
       </c>
       <c r="D218" t="n">
+        <v>-0.003838276209042083</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0.3063015383556713</v>
+      </c>
+      <c r="F218" t="n">
         <v>0.3101398145647133</v>
       </c>
     </row>
@@ -18053,6 +19365,12 @@
         <v>-0.3068746696986735</v>
       </c>
       <c r="D219" t="n">
+        <v>-1.399737243629702</v>
+      </c>
+      <c r="E219" t="n">
+        <v>-1.092862573931029</v>
+      </c>
+      <c r="F219" t="n">
         <v>0.3068746696986735</v>
       </c>
     </row>
@@ -18071,6 +19389,12 @@
         <v>-0.3041617603931976</v>
       </c>
       <c r="D220" t="n">
+        <v>-0.3603955616840646</v>
+      </c>
+      <c r="E220" t="n">
+        <v>-0.05623380129086705</v>
+      </c>
+      <c r="F220" t="n">
         <v>0.3041617603931976</v>
       </c>
     </row>
@@ -18089,6 +19413,12 @@
         <v>0.2976169822407597</v>
       </c>
       <c r="D221" t="n">
+        <v>0.241153407744334</v>
+      </c>
+      <c r="E221" t="n">
+        <v>-0.05646357449642567</v>
+      </c>
+      <c r="F221" t="n">
         <v>0.2976169822407597</v>
       </c>
     </row>
@@ -18107,6 +19437,12 @@
         <v>0.297391690855032</v>
       </c>
       <c r="D222" t="n">
+        <v>0.1306316530401642</v>
+      </c>
+      <c r="E222" t="n">
+        <v>-0.1667600378148678</v>
+      </c>
+      <c r="F222" t="n">
         <v>0.297391690855032</v>
       </c>
     </row>
@@ -18125,6 +19461,12 @@
         <v>0.2967925770569564</v>
       </c>
       <c r="D223" t="n">
+        <v>-0.1919198588157537</v>
+      </c>
+      <c r="E223" t="n">
+        <v>-0.48871243587271</v>
+      </c>
+      <c r="F223" t="n">
         <v>0.2967925770569564</v>
       </c>
     </row>
@@ -18143,6 +19485,12 @@
         <v>0.2952810825660553</v>
       </c>
       <c r="D224" t="n">
+        <v>-0.2019056992384069</v>
+      </c>
+      <c r="E224" t="n">
+        <v>-0.4971867818044622</v>
+      </c>
+      <c r="F224" t="n">
         <v>0.2952810825660553</v>
       </c>
     </row>
@@ -18161,6 +19509,12 @@
         <v>-0.2950184234536304</v>
       </c>
       <c r="D225" t="n">
+        <v>1.34735595731558</v>
+      </c>
+      <c r="E225" t="n">
+        <v>1.64237438076921</v>
+      </c>
+      <c r="F225" t="n">
         <v>0.2950184234536304</v>
       </c>
     </row>
@@ -18179,6 +19533,12 @@
         <v>0.2946721196359521</v>
       </c>
       <c r="D226" t="n">
+        <v>-0.08445502365197606</v>
+      </c>
+      <c r="E226" t="n">
+        <v>-0.3791271432879282</v>
+      </c>
+      <c r="F226" t="n">
         <v>0.2946721196359521</v>
       </c>
     </row>
@@ -18197,6 +19557,12 @@
         <v>0.2859521612822185</v>
       </c>
       <c r="D227" t="n">
+        <v>0.4611040065408153</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0.1751518452585969</v>
+      </c>
+      <c r="F227" t="n">
         <v>0.2859521612822185</v>
       </c>
     </row>
@@ -18215,6 +19581,12 @@
         <v>0.285756144287164</v>
       </c>
       <c r="D228" t="n">
+        <v>0.1751412732271536</v>
+      </c>
+      <c r="E228" t="n">
+        <v>-0.1106148710600104</v>
+      </c>
+      <c r="F228" t="n">
         <v>0.285756144287164</v>
       </c>
     </row>
@@ -18233,6 +19605,12 @@
         <v>-0.2853941788249365</v>
       </c>
       <c r="D229" t="n">
+        <v>-0.2289214886067876</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0.05647269021814889</v>
+      </c>
+      <c r="F229" t="n">
         <v>0.2853941788249365</v>
       </c>
     </row>
@@ -18251,6 +19629,12 @@
         <v>0.2853702185487261</v>
       </c>
       <c r="D230" t="n">
+        <v>-0.4054423133149249</v>
+      </c>
+      <c r="E230" t="n">
+        <v>-0.690812531863651</v>
+      </c>
+      <c r="F230" t="n">
         <v>0.2853702185487261</v>
       </c>
     </row>
@@ -18269,6 +19653,12 @@
         <v>0.28436716192016</v>
       </c>
       <c r="D231" t="n">
+        <v>1.381553398859416</v>
+      </c>
+      <c r="E231" t="n">
+        <v>1.097186236939256</v>
+      </c>
+      <c r="F231" t="n">
         <v>0.28436716192016</v>
       </c>
     </row>
@@ -18287,6 +19677,12 @@
         <v>0.2829839072311846</v>
       </c>
       <c r="D232" t="n">
+        <v>0.02039993438296779</v>
+      </c>
+      <c r="E232" t="n">
+        <v>-0.2625839728482168</v>
+      </c>
+      <c r="F232" t="n">
         <v>0.2829839072311846</v>
       </c>
     </row>
@@ -18305,6 +19701,12 @@
         <v>0.2799427996910441</v>
       </c>
       <c r="D233" t="n">
+        <v>0.2265658232972128</v>
+      </c>
+      <c r="E233" t="n">
+        <v>-0.05337697639383134</v>
+      </c>
+      <c r="F233" t="n">
         <v>0.2799427996910441</v>
       </c>
     </row>
@@ -18323,6 +19725,12 @@
         <v>0.2792615602886324</v>
       </c>
       <c r="D234" t="n">
+        <v>0.6756637231304699</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0.3964021628418375</v>
+      </c>
+      <c r="F234" t="n">
         <v>0.2792615602886324</v>
       </c>
     </row>
@@ -18341,6 +19749,12 @@
         <v>-0.2783062380148716</v>
       </c>
       <c r="D235" t="n">
+        <v>-0.100544996935459</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0.1777612410794126</v>
+      </c>
+      <c r="F235" t="n">
         <v>0.2783062380148716</v>
       </c>
     </row>
@@ -18359,6 +19773,12 @@
         <v>0.2758065090662278</v>
       </c>
       <c r="D236" t="n">
+        <v>0.1664490536651803</v>
+      </c>
+      <c r="E236" t="n">
+        <v>-0.1093574554010475</v>
+      </c>
+      <c r="F236" t="n">
         <v>0.2758065090662278</v>
       </c>
     </row>
@@ -18377,6 +19797,12 @@
         <v>-0.2746373576473792</v>
       </c>
       <c r="D237" t="n">
+        <v>-0.4617126191370313</v>
+      </c>
+      <c r="E237" t="n">
+        <v>-0.1870752614896522</v>
+      </c>
+      <c r="F237" t="n">
         <v>0.2746373576473792</v>
       </c>
     </row>
@@ -18395,6 +19821,12 @@
         <v>-0.2744436282396626</v>
       </c>
       <c r="D238" t="n">
+        <v>0.1701694712782645</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0.444613099517927</v>
+      </c>
+      <c r="F238" t="n">
         <v>0.2744436282396626</v>
       </c>
     </row>
@@ -18413,6 +19845,12 @@
         <v>-0.2743769750754372</v>
       </c>
       <c r="D239" t="n">
+        <v>-0.3002903080462394</v>
+      </c>
+      <c r="E239" t="n">
+        <v>-0.02591333297080215</v>
+      </c>
+      <c r="F239" t="n">
         <v>0.2743769750754372</v>
       </c>
     </row>
@@ -18431,6 +19869,12 @@
         <v>0.2729081470301856</v>
       </c>
       <c r="D240" t="n">
+        <v>0.9446621451660566</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0.671753998135871</v>
+      </c>
+      <c r="F240" t="n">
         <v>0.2729081470301856</v>
       </c>
     </row>
@@ -18449,6 +19893,12 @@
         <v>0.2727824646486079</v>
       </c>
       <c r="D241" t="n">
+        <v>0.3815863025643799</v>
+      </c>
+      <c r="E241" t="n">
+        <v>0.108803837915772</v>
+      </c>
+      <c r="F241" t="n">
         <v>0.2727824646486079</v>
       </c>
     </row>
@@ -18467,6 +19917,12 @@
         <v>0.2727560432694341</v>
       </c>
       <c r="D242" t="n">
+        <v>0.4546729429283725</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0.1819168996589383</v>
+      </c>
+      <c r="F242" t="n">
         <v>0.2727560432694341</v>
       </c>
     </row>
@@ -18485,6 +19941,12 @@
         <v>-0.2683692179947559</v>
       </c>
       <c r="D243" t="n">
+        <v>-0.1108347913868792</v>
+      </c>
+      <c r="E243" t="n">
+        <v>0.1575344266078767</v>
+      </c>
+      <c r="F243" t="n">
         <v>0.2683692179947559</v>
       </c>
     </row>
@@ -18503,6 +19965,12 @@
         <v>0.2663818816326645</v>
       </c>
       <c r="D244" t="n">
+        <v>-0.003061399363353801</v>
+      </c>
+      <c r="E244" t="n">
+        <v>-0.2694432809960183</v>
+      </c>
+      <c r="F244" t="n">
         <v>0.2663818816326645</v>
       </c>
     </row>
@@ -18521,6 +19989,12 @@
         <v>-0.2642457660214447</v>
       </c>
       <c r="D245" t="n">
+        <v>-0.230210568877555</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0.03403519714388967</v>
+      </c>
+      <c r="F245" t="n">
         <v>0.2642457660214447</v>
       </c>
     </row>
@@ -18539,6 +20013,12 @@
         <v>0.2616402349876443</v>
       </c>
       <c r="D246" t="n">
+        <v>0.6607534538502573</v>
+      </c>
+      <c r="E246" t="n">
+        <v>0.399113218862613</v>
+      </c>
+      <c r="F246" t="n">
         <v>0.2616402349876443</v>
       </c>
     </row>
@@ -18557,6 +20037,12 @@
         <v>0.2601274578966551</v>
       </c>
       <c r="D247" t="n">
+        <v>0.4969596234796251</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0.23683216558297</v>
+      </c>
+      <c r="F247" t="n">
         <v>0.2601274578966551</v>
       </c>
     </row>
@@ -18575,6 +20061,12 @@
         <v>0.2598573020706669</v>
       </c>
       <c r="D248" t="n">
+        <v>-1.152293816525977</v>
+      </c>
+      <c r="E248" t="n">
+        <v>-1.412151118596644</v>
+      </c>
+      <c r="F248" t="n">
         <v>0.2598573020706669</v>
       </c>
     </row>
@@ -18593,6 +20085,12 @@
         <v>0.2548374527286754</v>
       </c>
       <c r="D249" t="n">
+        <v>-0.1440821605972294</v>
+      </c>
+      <c r="E249" t="n">
+        <v>-0.3989196133259048</v>
+      </c>
+      <c r="F249" t="n">
         <v>0.2548374527286754</v>
       </c>
     </row>
@@ -18611,6 +20109,12 @@
         <v>-0.2501842840040996</v>
       </c>
       <c r="D250" t="n">
+        <v>-0.3654101893516196</v>
+      </c>
+      <c r="E250" t="n">
+        <v>-0.11522590534752</v>
+      </c>
+      <c r="F250" t="n">
         <v>0.2501842840040996</v>
       </c>
     </row>
@@ -18629,6 +20133,12 @@
         <v>0.2495894501789243</v>
       </c>
       <c r="D251" t="n">
+        <v>0.1865424577631232</v>
+      </c>
+      <c r="E251" t="n">
+        <v>-0.06304699241580107</v>
+      </c>
+      <c r="F251" t="n">
         <v>0.2495894501789243</v>
       </c>
     </row>
@@ -18647,6 +20157,12 @@
         <v>-0.2333862477779456</v>
       </c>
       <c r="D252" t="n">
+        <v>0.4928674087401846</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0.7262536565181302</v>
+      </c>
+      <c r="F252" t="n">
         <v>0.2333862477779456</v>
       </c>
     </row>
@@ -18665,6 +20181,12 @@
         <v>0.2314949516500367</v>
       </c>
       <c r="D253" t="n">
+        <v>0.1068539872133017</v>
+      </c>
+      <c r="E253" t="n">
+        <v>-0.124640964436735</v>
+      </c>
+      <c r="F253" t="n">
         <v>0.2314949516500367</v>
       </c>
     </row>
@@ -18683,6 +20205,12 @@
         <v>0.2261158651862712</v>
       </c>
       <c r="D254" t="n">
+        <v>0.04087309406430979</v>
+      </c>
+      <c r="E254" t="n">
+        <v>-0.1852427711219615</v>
+      </c>
+      <c r="F254" t="n">
         <v>0.2261158651862712</v>
       </c>
     </row>
@@ -18701,6 +20229,12 @@
         <v>0.2252885104327685</v>
       </c>
       <c r="D255" t="n">
+        <v>0.507266590275017</v>
+      </c>
+      <c r="E255" t="n">
+        <v>0.2819780798422484</v>
+      </c>
+      <c r="F255" t="n">
         <v>0.2252885104327685</v>
       </c>
     </row>
@@ -18719,6 +20253,12 @@
         <v>0.220699473194113</v>
       </c>
       <c r="D256" t="n">
+        <v>0.02126331389593083</v>
+      </c>
+      <c r="E256" t="n">
+        <v>-0.1994361592981822</v>
+      </c>
+      <c r="F256" t="n">
         <v>0.220699473194113</v>
       </c>
     </row>
@@ -18737,6 +20277,12 @@
         <v>0.2190488022247188</v>
       </c>
       <c r="D257" t="n">
+        <v>-0.03701970451214671</v>
+      </c>
+      <c r="E257" t="n">
+        <v>-0.2560685067368655</v>
+      </c>
+      <c r="F257" t="n">
         <v>0.2190488022247188</v>
       </c>
     </row>
@@ -18755,6 +20301,12 @@
         <v>-0.2169881150628405</v>
       </c>
       <c r="D258" t="n">
+        <v>0.5395683166501379</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0.7565564317129785</v>
+      </c>
+      <c r="F258" t="n">
         <v>0.2169881150628405</v>
       </c>
     </row>
@@ -18773,6 +20325,12 @@
         <v>-0.2162104539553482</v>
       </c>
       <c r="D259" t="n">
+        <v>17.99125977648784</v>
+      </c>
+      <c r="E259" t="n">
+        <v>18.20747023044319</v>
+      </c>
+      <c r="F259" t="n">
         <v>0.2162104539553482</v>
       </c>
     </row>
@@ -18791,6 +20349,12 @@
         <v>-0.2146056989771538</v>
       </c>
       <c r="D260" t="n">
+        <v>-0.2058802039544572</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0.008725495022696643</v>
+      </c>
+      <c r="F260" t="n">
         <v>0.2146056989771538</v>
       </c>
     </row>
@@ -18809,6 +20373,12 @@
         <v>0.2120566964105813</v>
       </c>
       <c r="D261" t="n">
+        <v>0.1693749989176377</v>
+      </c>
+      <c r="E261" t="n">
+        <v>-0.04268169749294359</v>
+      </c>
+      <c r="F261" t="n">
         <v>0.2120566964105813</v>
       </c>
     </row>
@@ -18827,6 +20397,12 @@
         <v>-0.2085656191238787</v>
       </c>
       <c r="D262" t="n">
+        <v>-0.192285283842403</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0.01628033528147574</v>
+      </c>
+      <c r="F262" t="n">
         <v>0.2085656191238787</v>
       </c>
     </row>
@@ -18845,6 +20421,12 @@
         <v>-0.2059558116618521</v>
       </c>
       <c r="D263" t="n">
+        <v>-0.2635423326931627</v>
+      </c>
+      <c r="E263" t="n">
+        <v>-0.05758652103131059</v>
+      </c>
+      <c r="F263" t="n">
         <v>0.2059558116618521</v>
       </c>
     </row>
@@ -18863,6 +20445,12 @@
         <v>-0.2047677966468411</v>
       </c>
       <c r="D264" t="n">
+        <v>-0.2920463337884329</v>
+      </c>
+      <c r="E264" t="n">
+        <v>-0.08727853714159185</v>
+      </c>
+      <c r="F264" t="n">
         <v>0.2047677966468411</v>
       </c>
     </row>
@@ -18881,6 +20469,12 @@
         <v>0.2026116041846758</v>
       </c>
       <c r="D265" t="n">
+        <v>-0.2495129766021583</v>
+      </c>
+      <c r="E265" t="n">
+        <v>-0.4521245807868341</v>
+      </c>
+      <c r="F265" t="n">
         <v>0.2026116041846758</v>
       </c>
     </row>
@@ -18899,6 +20493,12 @@
         <v>-0.2020504627599899</v>
       </c>
       <c r="D266" t="n">
+        <v>0.3787735858787061</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0.580824048638696</v>
+      </c>
+      <c r="F266" t="n">
         <v>0.2020504627599899</v>
       </c>
     </row>
@@ -18917,6 +20517,12 @@
         <v>0.1993264814204631</v>
       </c>
       <c r="D267" t="n">
+        <v>0.1588936016774866</v>
+      </c>
+      <c r="E267" t="n">
+        <v>-0.0404328797429765</v>
+      </c>
+      <c r="F267" t="n">
         <v>0.1993264814204631</v>
       </c>
     </row>
@@ -18935,6 +20541,12 @@
         <v>0.1977383565496268</v>
       </c>
       <c r="D268" t="n">
+        <v>-0.005346425298473506</v>
+      </c>
+      <c r="E268" t="n">
+        <v>-0.2030847818481003</v>
+      </c>
+      <c r="F268" t="n">
         <v>0.1977383565496268</v>
       </c>
     </row>
@@ -18953,6 +20565,12 @@
         <v>-0.1959134989472332</v>
       </c>
       <c r="D269" t="n">
+        <v>0.6574399291754003</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0.8533534281226335</v>
+      </c>
+      <c r="F269" t="n">
         <v>0.1959134989472332</v>
       </c>
     </row>
@@ -18971,6 +20589,12 @@
         <v>0.1837610914720212</v>
       </c>
       <c r="D270" t="n">
+        <v>0.2733762844906258</v>
+      </c>
+      <c r="E270" t="n">
+        <v>0.08961519301860461</v>
+      </c>
+      <c r="F270" t="n">
         <v>0.1837610914720212</v>
       </c>
     </row>
@@ -18989,6 +20613,12 @@
         <v>-0.1835992542785768</v>
       </c>
       <c r="D271" t="n">
+        <v>-0.3314111331840426</v>
+      </c>
+      <c r="E271" t="n">
+        <v>-0.1478118789054659</v>
+      </c>
+      <c r="F271" t="n">
         <v>0.1835992542785768</v>
       </c>
     </row>
@@ -19007,6 +20637,12 @@
         <v>-0.1832840815901392</v>
       </c>
       <c r="D272" t="n">
+        <v>-0.3507069532168017</v>
+      </c>
+      <c r="E272" t="n">
+        <v>-0.1674228716266625</v>
+      </c>
+      <c r="F272" t="n">
         <v>0.1832840815901392</v>
       </c>
     </row>
@@ -19025,6 +20661,12 @@
         <v>-0.1826813403381699</v>
       </c>
       <c r="D273" t="n">
+        <v>-0.3675873829772163</v>
+      </c>
+      <c r="E273" t="n">
+        <v>-0.1849060426390464</v>
+      </c>
+      <c r="F273" t="n">
         <v>0.1826813403381699</v>
       </c>
     </row>
@@ -19043,6 +20685,12 @@
         <v>0.1815222144420275</v>
       </c>
       <c r="D274" t="n">
+        <v>-0.2609723018275398</v>
+      </c>
+      <c r="E274" t="n">
+        <v>-0.4424945162695674</v>
+      </c>
+      <c r="F274" t="n">
         <v>0.1815222144420275</v>
       </c>
     </row>
@@ -19061,6 +20709,12 @@
         <v>0.1793505049424615</v>
       </c>
       <c r="D275" t="n">
+        <v>0.3571193452083636</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0.177768840265902</v>
+      </c>
+      <c r="F275" t="n">
         <v>0.1793505049424615</v>
       </c>
     </row>
@@ -19079,6 +20733,12 @@
         <v>0.1709200796979345</v>
       </c>
       <c r="D276" t="n">
+        <v>0.2171722578185271</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0.0462521781205926</v>
+      </c>
+      <c r="F276" t="n">
         <v>0.1709200796979345</v>
       </c>
     </row>
@@ -19097,6 +20757,12 @@
         <v>-0.1700259507304537</v>
       </c>
       <c r="D277" t="n">
+        <v>-0.2817823815626143</v>
+      </c>
+      <c r="E277" t="n">
+        <v>-0.1117564308321606</v>
+      </c>
+      <c r="F277" t="n">
         <v>0.1700259507304537</v>
       </c>
     </row>
@@ -19115,6 +20781,12 @@
         <v>0.1698048074700024</v>
       </c>
       <c r="D278" t="n">
+        <v>0.04949197427203385</v>
+      </c>
+      <c r="E278" t="n">
+        <v>-0.1203128331979686</v>
+      </c>
+      <c r="F278" t="n">
         <v>0.1698048074700024</v>
       </c>
     </row>
@@ -19133,6 +20805,12 @@
         <v>-0.1665809988806594</v>
       </c>
       <c r="D279" t="n">
+        <v>-0.1665809988806594</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+      <c r="F279" t="n">
         <v>0.1665809988806594</v>
       </c>
     </row>
@@ -19151,6 +20829,12 @@
         <v>-0.1658213644142187</v>
       </c>
       <c r="D280" t="n">
+        <v>-0.2249417934861938</v>
+      </c>
+      <c r="E280" t="n">
+        <v>-0.05912042907197509</v>
+      </c>
+      <c r="F280" t="n">
         <v>0.1658213644142187</v>
       </c>
     </row>
@@ -19169,6 +20853,12 @@
         <v>-0.1655767268842948</v>
       </c>
       <c r="D281" t="n">
+        <v>-0.2866391262832105</v>
+      </c>
+      <c r="E281" t="n">
+        <v>-0.1210623993989157</v>
+      </c>
+      <c r="F281" t="n">
         <v>0.1655767268842948</v>
       </c>
     </row>
@@ -19187,6 +20877,12 @@
         <v>-0.1632837367285589</v>
       </c>
       <c r="D282" t="n">
+        <v>0.2273268787845882</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0.3906106155131471</v>
+      </c>
+      <c r="F282" t="n">
         <v>0.1632837367285589</v>
       </c>
     </row>
@@ -19205,6 +20901,12 @@
         <v>-0.1618744197779982</v>
       </c>
       <c r="D283" t="n">
+        <v>-0.02013311225655057</v>
+      </c>
+      <c r="E283" t="n">
+        <v>0.1417413075214476</v>
+      </c>
+      <c r="F283" t="n">
         <v>0.1618744197779982</v>
       </c>
     </row>
@@ -19223,6 +20925,12 @@
         <v>-0.1614339342219221</v>
       </c>
       <c r="D284" t="n">
+        <v>-0.1437853846149748</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0.01764854960694735</v>
+      </c>
+      <c r="F284" t="n">
         <v>0.1614339342219221</v>
       </c>
     </row>
@@ -19241,6 +20949,12 @@
         <v>-0.1571186746118566</v>
       </c>
       <c r="D285" t="n">
+        <v>-0.2658758690624375</v>
+      </c>
+      <c r="E285" t="n">
+        <v>-0.1087571944505809</v>
+      </c>
+      <c r="F285" t="n">
         <v>0.1571186746118566</v>
       </c>
     </row>
@@ -19259,6 +20973,12 @@
         <v>-0.1545475635046443</v>
       </c>
       <c r="D286" t="n">
+        <v>0.6377176361287727</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0.792265199633417</v>
+      </c>
+      <c r="F286" t="n">
         <v>0.1545475635046443</v>
       </c>
     </row>
@@ -19277,6 +20997,12 @@
         <v>-0.154492201620195</v>
       </c>
       <c r="D287" t="n">
+        <v>-0.1773623983067213</v>
+      </c>
+      <c r="E287" t="n">
+        <v>-0.02287019668652634</v>
+      </c>
+      <c r="F287" t="n">
         <v>0.154492201620195</v>
       </c>
     </row>
@@ -19295,6 +21021,12 @@
         <v>0.1536596185264634</v>
       </c>
       <c r="D288" t="n">
+        <v>0.3282851100648604</v>
+      </c>
+      <c r="E288" t="n">
+        <v>0.174625491538397</v>
+      </c>
+      <c r="F288" t="n">
         <v>0.1536596185264634</v>
       </c>
     </row>
@@ -19313,6 +21045,12 @@
         <v>0.1530076650449854</v>
       </c>
       <c r="D289" t="n">
+        <v>-0.2112246048507772</v>
+      </c>
+      <c r="E289" t="n">
+        <v>-0.3642322698957626</v>
+      </c>
+      <c r="F289" t="n">
         <v>0.1530076650449854</v>
       </c>
     </row>
@@ -19331,6 +21069,12 @@
         <v>-0.1522797741155439</v>
       </c>
       <c r="D290" t="n">
+        <v>-0.06252084224408898</v>
+      </c>
+      <c r="E290" t="n">
+        <v>0.08975893187145494</v>
+      </c>
+      <c r="F290" t="n">
         <v>0.1522797741155439</v>
       </c>
     </row>
@@ -19349,6 +21093,12 @@
         <v>-0.1466770262872782</v>
       </c>
       <c r="D291" t="n">
+        <v>0.05747898932548484</v>
+      </c>
+      <c r="E291" t="n">
+        <v>0.204156015612763</v>
+      </c>
+      <c r="F291" t="n">
         <v>0.1466770262872782</v>
       </c>
     </row>
@@ -19367,6 +21117,12 @@
         <v>0.1466024609069456</v>
       </c>
       <c r="D292" t="n">
+        <v>-0.1005037815259215</v>
+      </c>
+      <c r="E292" t="n">
+        <v>-0.2471062424328671</v>
+      </c>
+      <c r="F292" t="n">
         <v>0.1466024609069456</v>
       </c>
     </row>
@@ -19385,6 +21141,12 @@
         <v>0.1463628906739624</v>
       </c>
       <c r="D293" t="n">
+        <v>-0.1523998202653174</v>
+      </c>
+      <c r="E293" t="n">
+        <v>-0.2987627109392798</v>
+      </c>
+      <c r="F293" t="n">
         <v>0.1463628906739624</v>
       </c>
     </row>
@@ -19403,6 +21165,12 @@
         <v>0.1449759779267902</v>
       </c>
       <c r="D294" t="n">
+        <v>-0.7163228132724452</v>
+      </c>
+      <c r="E294" t="n">
+        <v>-0.8612987911992354</v>
+      </c>
+      <c r="F294" t="n">
         <v>0.1449759779267902</v>
       </c>
     </row>
@@ -19421,6 +21189,12 @@
         <v>-0.144645543499076</v>
       </c>
       <c r="D295" t="n">
+        <v>-0.2697751379297908</v>
+      </c>
+      <c r="E295" t="n">
+        <v>-0.1251295944307148</v>
+      </c>
+      <c r="F295" t="n">
         <v>0.144645543499076</v>
       </c>
     </row>
@@ -19439,6 +21213,12 @@
         <v>0.1431038336823722</v>
       </c>
       <c r="D296" t="n">
+        <v>0.3116238581270818</v>
+      </c>
+      <c r="E296" t="n">
+        <v>0.1685200244447096</v>
+      </c>
+      <c r="F296" t="n">
         <v>0.1431038336823722</v>
       </c>
     </row>
@@ -19457,6 +21237,12 @@
         <v>-0.1421808507622758</v>
       </c>
       <c r="D297" t="n">
+        <v>-0.2310144798821922</v>
+      </c>
+      <c r="E297" t="n">
+        <v>-0.08883362911991642</v>
+      </c>
+      <c r="F297" t="n">
         <v>0.1421808507622758</v>
       </c>
     </row>
@@ -19475,6 +21261,12 @@
         <v>-0.1415847953594687</v>
       </c>
       <c r="D298" t="n">
+        <v>-0.3381948398325643</v>
+      </c>
+      <c r="E298" t="n">
+        <v>-0.1966100444730956</v>
+      </c>
+      <c r="F298" t="n">
         <v>0.1415847953594687</v>
       </c>
     </row>
@@ -19493,6 +21285,12 @@
         <v>-0.1406159163554556</v>
       </c>
       <c r="D299" t="n">
+        <v>-0.1944330215400147</v>
+      </c>
+      <c r="E299" t="n">
+        <v>-0.05381710518455907</v>
+      </c>
+      <c r="F299" t="n">
         <v>0.1406159163554556</v>
       </c>
     </row>
@@ -19511,6 +21309,12 @@
         <v>0.1382059740576716</v>
       </c>
       <c r="D300" t="n">
+        <v>0.2920790801463445</v>
+      </c>
+      <c r="E300" t="n">
+        <v>0.1538731060886729</v>
+      </c>
+      <c r="F300" t="n">
         <v>0.1382059740576716</v>
       </c>
     </row>
@@ -19529,6 +21333,12 @@
         <v>0.1347716681093134</v>
       </c>
       <c r="D301" t="n">
+        <v>-0.4169477016405817</v>
+      </c>
+      <c r="E301" t="n">
+        <v>-0.5517193697498951</v>
+      </c>
+      <c r="F301" t="n">
         <v>0.1347716681093134</v>
       </c>
     </row>
@@ -19547,6 +21357,12 @@
         <v>0.1333560710910039</v>
       </c>
       <c r="D302" t="n">
+        <v>0.6688132258973658</v>
+      </c>
+      <c r="E302" t="n">
+        <v>0.5354571548063619</v>
+      </c>
+      <c r="F302" t="n">
         <v>0.1333560710910039</v>
       </c>
     </row>
@@ -19565,6 +21381,12 @@
         <v>-0.1322634058502113</v>
       </c>
       <c r="D303" t="n">
+        <v>-0.3675827503325362</v>
+      </c>
+      <c r="E303" t="n">
+        <v>-0.2353193444823249</v>
+      </c>
+      <c r="F303" t="n">
         <v>0.1322634058502113</v>
       </c>
     </row>
@@ -19583,6 +21405,12 @@
         <v>-0.1322352628386428</v>
       </c>
       <c r="D304" t="n">
+        <v>-0.1606074918380992</v>
+      </c>
+      <c r="E304" t="n">
+        <v>-0.02837222899945646</v>
+      </c>
+      <c r="F304" t="n">
         <v>0.1322352628386428</v>
       </c>
     </row>
@@ -19601,6 +21429,12 @@
         <v>0.1303749640821513</v>
       </c>
       <c r="D305" t="n">
+        <v>0.4556691256421123</v>
+      </c>
+      <c r="E305" t="n">
+        <v>0.325294161559961</v>
+      </c>
+      <c r="F305" t="n">
         <v>0.1303749640821513</v>
       </c>
     </row>
@@ -19619,6 +21453,12 @@
         <v>0.1269573903225663</v>
       </c>
       <c r="D306" t="n">
+        <v>-0.06337242505244768</v>
+      </c>
+      <c r="E306" t="n">
+        <v>-0.1903298153750139</v>
+      </c>
+      <c r="F306" t="n">
         <v>0.1269573903225663</v>
       </c>
     </row>
@@ -19637,6 +21477,12 @@
         <v>-0.1252391677399289</v>
       </c>
       <c r="D307" t="n">
+        <v>0.01814047168025615</v>
+      </c>
+      <c r="E307" t="n">
+        <v>0.1433796394201851</v>
+      </c>
+      <c r="F307" t="n">
         <v>0.1252391677399289</v>
       </c>
     </row>
@@ -19655,6 +21501,12 @@
         <v>0.1228197861527098</v>
       </c>
       <c r="D308" t="n">
+        <v>0.5214126700038887</v>
+      </c>
+      <c r="E308" t="n">
+        <v>0.3985928838511789</v>
+      </c>
+      <c r="F308" t="n">
         <v>0.1228197861527098</v>
       </c>
     </row>
@@ -19673,6 +21525,12 @@
         <v>0.1219782234732272</v>
       </c>
       <c r="D309" t="n">
+        <v>-0.09163114996483229</v>
+      </c>
+      <c r="E309" t="n">
+        <v>-0.2136093734380595</v>
+      </c>
+      <c r="F309" t="n">
         <v>0.1219782234732272</v>
       </c>
     </row>
@@ -19691,6 +21549,12 @@
         <v>0.1209799674926136</v>
       </c>
       <c r="D310" t="n">
+        <v>-0.4061267395239696</v>
+      </c>
+      <c r="E310" t="n">
+        <v>-0.5271067070165832</v>
+      </c>
+      <c r="F310" t="n">
         <v>0.1209799674926136</v>
       </c>
     </row>
@@ -19709,6 +21573,12 @@
         <v>-0.1200697338359288</v>
       </c>
       <c r="D311" t="n">
+        <v>0.1765526406227035</v>
+      </c>
+      <c r="E311" t="n">
+        <v>0.2966223744586323</v>
+      </c>
+      <c r="F311" t="n">
         <v>0.1200697338359288</v>
       </c>
     </row>
@@ -19727,6 +21597,12 @@
         <v>-0.1193454792289123</v>
       </c>
       <c r="D312" t="n">
+        <v>-0.02385073334302157</v>
+      </c>
+      <c r="E312" t="n">
+        <v>0.09549474588589069</v>
+      </c>
+      <c r="F312" t="n">
         <v>0.1193454792289123</v>
       </c>
     </row>
@@ -19745,6 +21621,12 @@
         <v>-0.1178942744216483</v>
       </c>
       <c r="D313" t="n">
+        <v>-0.1876078019982099</v>
+      </c>
+      <c r="E313" t="n">
+        <v>-0.06971352757656164</v>
+      </c>
+      <c r="F313" t="n">
         <v>0.1178942744216483</v>
       </c>
     </row>
@@ -19763,6 +21645,12 @@
         <v>0.1170498903688554</v>
       </c>
       <c r="D314" t="n">
+        <v>-0.2001015722926477</v>
+      </c>
+      <c r="E314" t="n">
+        <v>-0.3171514626615031</v>
+      </c>
+      <c r="F314" t="n">
         <v>0.1170498903688554</v>
       </c>
     </row>
@@ -19781,6 +21669,12 @@
         <v>-0.11672962867881</v>
       </c>
       <c r="D315" t="n">
+        <v>-0.1756404897048292</v>
+      </c>
+      <c r="E315" t="n">
+        <v>-0.05891086102601918</v>
+      </c>
+      <c r="F315" t="n">
         <v>0.11672962867881</v>
       </c>
     </row>
@@ -19799,6 +21693,12 @@
         <v>0.1130625572660642</v>
       </c>
       <c r="D316" t="n">
+        <v>1.885085754737602</v>
+      </c>
+      <c r="E316" t="n">
+        <v>1.772023197471538</v>
+      </c>
+      <c r="F316" t="n">
         <v>0.1130625572660642</v>
       </c>
     </row>
@@ -19817,6 +21717,12 @@
         <v>0.1130231143917047</v>
       </c>
       <c r="D317" t="n">
+        <v>-0.1113221636655019</v>
+      </c>
+      <c r="E317" t="n">
+        <v>-0.2243452780572066</v>
+      </c>
+      <c r="F317" t="n">
         <v>0.1130231143917047</v>
       </c>
     </row>
@@ -19835,6 +21741,12 @@
         <v>-0.1107983951190278</v>
       </c>
       <c r="D318" t="n">
+        <v>-0.2262357177518183</v>
+      </c>
+      <c r="E318" t="n">
+        <v>-0.1154373226327906</v>
+      </c>
+      <c r="F318" t="n">
         <v>0.1107983951190278</v>
       </c>
     </row>
@@ -19853,6 +21765,12 @@
         <v>0.1041774781260436</v>
       </c>
       <c r="D319" t="n">
+        <v>-0.7033010034321914</v>
+      </c>
+      <c r="E319" t="n">
+        <v>-0.807478481558235</v>
+      </c>
+      <c r="F319" t="n">
         <v>0.1041774781260436</v>
       </c>
     </row>
@@ -19871,6 +21789,12 @@
         <v>0.1022953605854504</v>
       </c>
       <c r="D320" t="n">
+        <v>0.05699385360626611</v>
+      </c>
+      <c r="E320" t="n">
+        <v>-0.04530150697918426</v>
+      </c>
+      <c r="F320" t="n">
         <v>0.1022953605854504</v>
       </c>
     </row>
@@ -19889,6 +21813,12 @@
         <v>-0.09935091734375778</v>
       </c>
       <c r="D321" t="n">
+        <v>0.03357425642025256</v>
+      </c>
+      <c r="E321" t="n">
+        <v>0.1329251737640103</v>
+      </c>
+      <c r="F321" t="n">
         <v>0.09935091734375778</v>
       </c>
     </row>
@@ -19907,6 +21837,12 @@
         <v>-0.09886516609895371</v>
       </c>
       <c r="D322" t="n">
+        <v>-0.1537197655528167</v>
+      </c>
+      <c r="E322" t="n">
+        <v>-0.054854599453863</v>
+      </c>
+      <c r="F322" t="n">
         <v>0.09886516609895371</v>
       </c>
     </row>
@@ -19925,6 +21861,12 @@
         <v>0.09331767178502715</v>
       </c>
       <c r="D323" t="n">
+        <v>0.5570282458025604</v>
+      </c>
+      <c r="E323" t="n">
+        <v>0.4637105740175332</v>
+      </c>
+      <c r="F323" t="n">
         <v>0.09331767178502715</v>
       </c>
     </row>
@@ -19943,6 +21885,12 @@
         <v>-0.09181574004944106</v>
       </c>
       <c r="D324" t="n">
+        <v>0.04223898314981507</v>
+      </c>
+      <c r="E324" t="n">
+        <v>0.1340547231992561</v>
+      </c>
+      <c r="F324" t="n">
         <v>0.09181574004944106</v>
       </c>
     </row>
@@ -19961,6 +21909,12 @@
         <v>0.08980265101338718</v>
       </c>
       <c r="D325" t="n">
+        <v>0</v>
+      </c>
+      <c r="E325" t="n">
+        <v>-0.08980265101338718</v>
+      </c>
+      <c r="F325" t="n">
         <v>0.08980265101338718</v>
       </c>
     </row>
@@ -19979,6 +21933,12 @@
         <v>-0.08601909096710714</v>
       </c>
       <c r="D326" t="n">
+        <v>0.3458283760170001</v>
+      </c>
+      <c r="E326" t="n">
+        <v>0.4318474669841073</v>
+      </c>
+      <c r="F326" t="n">
         <v>0.08601909096710714</v>
       </c>
     </row>
@@ -19997,6 +21957,12 @@
         <v>0.08533533315143108</v>
       </c>
       <c r="D327" t="n">
+        <v>0.2140314553655585</v>
+      </c>
+      <c r="E327" t="n">
+        <v>0.1286961222141274</v>
+      </c>
+      <c r="F327" t="n">
         <v>0.08533533315143108</v>
       </c>
     </row>
@@ -20015,6 +21981,12 @@
         <v>-0.08263266857882862</v>
       </c>
       <c r="D328" t="n">
+        <v>-0.3356918648699239</v>
+      </c>
+      <c r="E328" t="n">
+        <v>-0.2530591962910953</v>
+      </c>
+      <c r="F328" t="n">
         <v>0.08263266857882862</v>
       </c>
     </row>
@@ -20033,6 +22005,12 @@
         <v>0.08127582208016138</v>
       </c>
       <c r="D329" t="n">
+        <v>0.7936427130022052</v>
+      </c>
+      <c r="E329" t="n">
+        <v>0.7123668909220439</v>
+      </c>
+      <c r="F329" t="n">
         <v>0.08127582208016138</v>
       </c>
     </row>
@@ -20051,6 +22029,12 @@
         <v>-0.07601831109076673</v>
       </c>
       <c r="D330" t="n">
+        <v>0.9069901688757911</v>
+      </c>
+      <c r="E330" t="n">
+        <v>0.9830084799665578</v>
+      </c>
+      <c r="F330" t="n">
         <v>0.07601831109076673</v>
       </c>
     </row>
@@ -20069,6 +22053,12 @@
         <v>0.06934066406737391</v>
       </c>
       <c r="D331" t="n">
+        <v>0.1763877075947504</v>
+      </c>
+      <c r="E331" t="n">
+        <v>0.1070470435273765</v>
+      </c>
+      <c r="F331" t="n">
         <v>0.06934066406737391</v>
       </c>
     </row>
@@ -20087,6 +22077,12 @@
         <v>0.06833535200547938</v>
       </c>
       <c r="D332" t="n">
+        <v>-0.01613778431801358</v>
+      </c>
+      <c r="E332" t="n">
+        <v>-0.08447313632349297</v>
+      </c>
+      <c r="F332" t="n">
         <v>0.06833535200547938</v>
       </c>
     </row>
@@ -20105,6 +22101,12 @@
         <v>-0.06644962948872743</v>
       </c>
       <c r="D333" t="n">
+        <v>-0.2264332960492666</v>
+      </c>
+      <c r="E333" t="n">
+        <v>-0.1599836665605392</v>
+      </c>
+      <c r="F333" t="n">
         <v>0.06644962948872743</v>
       </c>
     </row>
@@ -20123,6 +22125,12 @@
         <v>0.06638587893694373</v>
       </c>
       <c r="D334" t="n">
+        <v>-0.216571006095782</v>
+      </c>
+      <c r="E334" t="n">
+        <v>-0.2829568850327258</v>
+      </c>
+      <c r="F334" t="n">
         <v>0.06638587893694373</v>
       </c>
     </row>
@@ -20141,6 +22149,12 @@
         <v>-0.06621786093035287</v>
       </c>
       <c r="D335" t="n">
+        <v>-0.5577352312388151</v>
+      </c>
+      <c r="E335" t="n">
+        <v>-0.4915173703084622</v>
+      </c>
+      <c r="F335" t="n">
         <v>0.06621786093035287</v>
       </c>
     </row>
@@ -20159,6 +22173,12 @@
         <v>0.06505073300454828</v>
       </c>
       <c r="D336" t="n">
+        <v>0.3716804775493166</v>
+      </c>
+      <c r="E336" t="n">
+        <v>0.3066297445447683</v>
+      </c>
+      <c r="F336" t="n">
         <v>0.06505073300454828</v>
       </c>
     </row>
@@ -20177,6 +22197,12 @@
         <v>-0.06398189234721485</v>
       </c>
       <c r="D337" t="n">
+        <v>-0.5138421984924511</v>
+      </c>
+      <c r="E337" t="n">
+        <v>-0.4498603061452362</v>
+      </c>
+      <c r="F337" t="n">
         <v>0.06398189234721485</v>
       </c>
     </row>
@@ -20195,6 +22221,12 @@
         <v>0.06278256219057457</v>
       </c>
       <c r="D338" t="n">
+        <v>-0.02973044721798226</v>
+      </c>
+      <c r="E338" t="n">
+        <v>-0.09251300940855683</v>
+      </c>
+      <c r="F338" t="n">
         <v>0.06278256219057457</v>
       </c>
     </row>
@@ -20213,6 +22245,12 @@
         <v>-0.06146890201393805</v>
       </c>
       <c r="D339" t="n">
+        <v>-0.123403510468458</v>
+      </c>
+      <c r="E339" t="n">
+        <v>-0.06193460845451999</v>
+      </c>
+      <c r="F339" t="n">
         <v>0.06146890201393805</v>
       </c>
     </row>
@@ -20231,6 +22269,12 @@
         <v>0.06135803337099982</v>
       </c>
       <c r="D340" t="n">
+        <v>-0.2158043245867361</v>
+      </c>
+      <c r="E340" t="n">
+        <v>-0.2771623579577359</v>
+      </c>
+      <c r="F340" t="n">
         <v>0.06135803337099982</v>
       </c>
     </row>
@@ -20249,6 +22293,12 @@
         <v>-0.06105911951173409</v>
       </c>
       <c r="D341" t="n">
+        <v>0.1589876272709041</v>
+      </c>
+      <c r="E341" t="n">
+        <v>0.2200467467826382</v>
+      </c>
+      <c r="F341" t="n">
         <v>0.06105911951173409</v>
       </c>
     </row>
@@ -20267,6 +22317,12 @@
         <v>0.05935779362340279</v>
       </c>
       <c r="D342" t="n">
+        <v>0</v>
+      </c>
+      <c r="E342" t="n">
+        <v>-0.05935779362340279</v>
+      </c>
+      <c r="F342" t="n">
         <v>0.05935779362340279</v>
       </c>
     </row>
@@ -20285,6 +22341,12 @@
         <v>0.05935245782037632</v>
       </c>
       <c r="D343" t="n">
+        <v>-0.2222849161541185</v>
+      </c>
+      <c r="E343" t="n">
+        <v>-0.2816373739744948</v>
+      </c>
+      <c r="F343" t="n">
         <v>0.05935245782037632</v>
       </c>
     </row>
@@ -20303,6 +22365,12 @@
         <v>-0.05891149875208367</v>
       </c>
       <c r="D344" t="n">
+        <v>-0.1717752993121552</v>
+      </c>
+      <c r="E344" t="n">
+        <v>-0.1128638005600715</v>
+      </c>
+      <c r="F344" t="n">
         <v>0.05891149875208367</v>
       </c>
     </row>
@@ -20321,6 +22389,12 @@
         <v>-0.0569908484927834</v>
       </c>
       <c r="D345" t="n">
+        <v>0.04541868208290006</v>
+      </c>
+      <c r="E345" t="n">
+        <v>0.1024095305756835</v>
+      </c>
+      <c r="F345" t="n">
         <v>0.0569908484927834</v>
       </c>
     </row>
@@ -20339,6 +22413,12 @@
         <v>0.056620349335191</v>
       </c>
       <c r="D346" t="n">
+        <v>0.1991448703682874</v>
+      </c>
+      <c r="E346" t="n">
+        <v>0.1425245210330964</v>
+      </c>
+      <c r="F346" t="n">
         <v>0.056620349335191</v>
       </c>
     </row>
@@ -20357,6 +22437,12 @@
         <v>-0.05308617182410118</v>
       </c>
       <c r="D347" t="n">
+        <v>-0.009361089580401747</v>
+      </c>
+      <c r="E347" t="n">
+        <v>0.04372508224369943</v>
+      </c>
+      <c r="F347" t="n">
         <v>0.05308617182410118</v>
       </c>
     </row>
@@ -20375,6 +22461,12 @@
         <v>-0.05168926483137293</v>
       </c>
       <c r="D348" t="n">
+        <v>1.114931313154891</v>
+      </c>
+      <c r="E348" t="n">
+        <v>1.166620577986264</v>
+      </c>
+      <c r="F348" t="n">
         <v>0.05168926483137293</v>
       </c>
     </row>
@@ -20393,6 +22485,12 @@
         <v>0.04813036951415428</v>
       </c>
       <c r="D349" t="n">
+        <v>0.7578853887018705</v>
+      </c>
+      <c r="E349" t="n">
+        <v>0.7097550191877162</v>
+      </c>
+      <c r="F349" t="n">
         <v>0.04813036951415428</v>
       </c>
     </row>
@@ -20411,6 +22509,12 @@
         <v>-0.04466927757617671</v>
       </c>
       <c r="D350" t="n">
+        <v>-0.1312365506911784</v>
+      </c>
+      <c r="E350" t="n">
+        <v>-0.08656727311500166</v>
+      </c>
+      <c r="F350" t="n">
         <v>0.04466927757617671</v>
       </c>
     </row>
@@ -20429,6 +22533,12 @@
         <v>0.04243136916961465</v>
       </c>
       <c r="D351" t="n">
+        <v>0.4662210916138665</v>
+      </c>
+      <c r="E351" t="n">
+        <v>0.4237897224442518</v>
+      </c>
+      <c r="F351" t="n">
         <v>0.04243136916961465</v>
       </c>
     </row>
@@ -20447,6 +22557,12 @@
         <v>-0.0392690724627483</v>
       </c>
       <c r="D352" t="n">
+        <v>0.3816466469992851</v>
+      </c>
+      <c r="E352" t="n">
+        <v>0.4209157194620334</v>
+      </c>
+      <c r="F352" t="n">
         <v>0.0392690724627483</v>
       </c>
     </row>
@@ -20465,6 +22581,12 @@
         <v>-0.03865949660035595</v>
       </c>
       <c r="D353" t="n">
+        <v>0.6137490227867534</v>
+      </c>
+      <c r="E353" t="n">
+        <v>0.6524085193871093</v>
+      </c>
+      <c r="F353" t="n">
         <v>0.03865949660035595</v>
       </c>
     </row>
@@ -20483,6 +22605,12 @@
         <v>-0.03780331212826113</v>
       </c>
       <c r="D354" t="n">
+        <v>0.2048545299342615</v>
+      </c>
+      <c r="E354" t="n">
+        <v>0.2426578420625226</v>
+      </c>
+      <c r="F354" t="n">
         <v>0.03780331212826113</v>
       </c>
     </row>
@@ -20501,6 +22629,12 @@
         <v>0.03709009600412072</v>
       </c>
       <c r="D355" t="n">
+        <v>0.02391962420083865</v>
+      </c>
+      <c r="E355" t="n">
+        <v>-0.01317047180328207</v>
+      </c>
+      <c r="F355" t="n">
         <v>0.03709009600412072</v>
       </c>
     </row>
@@ -20519,6 +22653,12 @@
         <v>-0.03704108558299848</v>
       </c>
       <c r="D356" t="n">
+        <v>-0.202894565099692</v>
+      </c>
+      <c r="E356" t="n">
+        <v>-0.1658534795166935</v>
+      </c>
+      <c r="F356" t="n">
         <v>0.03704108558299848</v>
       </c>
     </row>
@@ -20537,6 +22677,12 @@
         <v>0.03671869360154767</v>
       </c>
       <c r="D357" t="n">
+        <v>-0.6509161027390292</v>
+      </c>
+      <c r="E357" t="n">
+        <v>-0.6876347963405769</v>
+      </c>
+      <c r="F357" t="n">
         <v>0.03671869360154767</v>
       </c>
     </row>
@@ -20555,6 +22701,12 @@
         <v>0.03481997439130749</v>
       </c>
       <c r="D358" t="n">
+        <v>0.1724060428979473</v>
+      </c>
+      <c r="E358" t="n">
+        <v>0.1375860685066398</v>
+      </c>
+      <c r="F358" t="n">
         <v>0.03481997439130749</v>
       </c>
     </row>
@@ -20573,6 +22725,12 @@
         <v>-0.03326320581801484</v>
       </c>
       <c r="D359" t="n">
+        <v>-0.3304905148731558</v>
+      </c>
+      <c r="E359" t="n">
+        <v>-0.297227309055141</v>
+      </c>
+      <c r="F359" t="n">
         <v>0.03326320581801484</v>
       </c>
     </row>
@@ -20591,6 +22749,12 @@
         <v>-0.02804038015054766</v>
       </c>
       <c r="D360" t="n">
+        <v>-0.1732047460313745</v>
+      </c>
+      <c r="E360" t="n">
+        <v>-0.1451643658808268</v>
+      </c>
+      <c r="F360" t="n">
         <v>0.02804038015054766</v>
       </c>
     </row>
@@ -20609,6 +22773,12 @@
         <v>-0.02405886718924444</v>
       </c>
       <c r="D361" t="n">
+        <v>-0.6439482720363809</v>
+      </c>
+      <c r="E361" t="n">
+        <v>-0.6198894048471365</v>
+      </c>
+      <c r="F361" t="n">
         <v>0.02405886718924444</v>
       </c>
     </row>
@@ -20627,6 +22797,12 @@
         <v>-0.02227530908435593</v>
       </c>
       <c r="D362" t="n">
+        <v>0.815097113829821</v>
+      </c>
+      <c r="E362" t="n">
+        <v>0.8373724229141769</v>
+      </c>
+      <c r="F362" t="n">
         <v>0.02227530908435593</v>
       </c>
     </row>
@@ -20645,6 +22821,12 @@
         <v>0.01914973714816681</v>
       </c>
       <c r="D363" t="n">
+        <v>0.1762933089070038</v>
+      </c>
+      <c r="E363" t="n">
+        <v>0.157143571758837</v>
+      </c>
+      <c r="F363" t="n">
         <v>0.01914973714816681</v>
       </c>
     </row>
@@ -20663,6 +22845,12 @@
         <v>-0.01773067389807303</v>
       </c>
       <c r="D364" t="n">
+        <v>-0.3816034255919065</v>
+      </c>
+      <c r="E364" t="n">
+        <v>-0.3638727516938335</v>
+      </c>
+      <c r="F364" t="n">
         <v>0.01773067389807303</v>
       </c>
     </row>
@@ -20681,6 +22869,12 @@
         <v>0.01719134024391675</v>
       </c>
       <c r="D365" t="n">
+        <v>-0.2260879156586427</v>
+      </c>
+      <c r="E365" t="n">
+        <v>-0.2432792559025594</v>
+      </c>
+      <c r="F365" t="n">
         <v>0.01719134024391675</v>
       </c>
     </row>
@@ -20699,6 +22893,12 @@
         <v>-0.0151215498443058</v>
       </c>
       <c r="D366" t="n">
+        <v>-0.1149070777601336</v>
+      </c>
+      <c r="E366" t="n">
+        <v>-0.09978552791582777</v>
+      </c>
+      <c r="F366" t="n">
         <v>0.0151215498443058</v>
       </c>
     </row>
@@ -20717,6 +22917,12 @@
         <v>-0.01347106588328827</v>
       </c>
       <c r="D367" t="n">
+        <v>0.07900873790103657</v>
+      </c>
+      <c r="E367" t="n">
+        <v>0.09247980378432484</v>
+      </c>
+      <c r="F367" t="n">
         <v>0.01347106588328827</v>
       </c>
     </row>
@@ -20735,6 +22941,12 @@
         <v>0.01256727227589657</v>
       </c>
       <c r="D368" t="n">
+        <v>-0.1789246541521492</v>
+      </c>
+      <c r="E368" t="n">
+        <v>-0.1914919264280457</v>
+      </c>
+      <c r="F368" t="n">
         <v>0.01256727227589657</v>
       </c>
     </row>
@@ -20753,6 +22965,12 @@
         <v>0.01001362842763509</v>
       </c>
       <c r="D369" t="n">
+        <v>-0.2401716222983689</v>
+      </c>
+      <c r="E369" t="n">
+        <v>-0.250185250726004</v>
+      </c>
+      <c r="F369" t="n">
         <v>0.01001362842763509</v>
       </c>
     </row>
@@ -20771,6 +22989,12 @@
         <v>-0.009516408895768325</v>
       </c>
       <c r="D370" t="n">
+        <v>0.05329084857227498</v>
+      </c>
+      <c r="E370" t="n">
+        <v>0.0628072574680433</v>
+      </c>
+      <c r="F370" t="n">
         <v>0.009516408895768325</v>
       </c>
     </row>
@@ -20789,6 +23013,12 @@
         <v>0.009186796141091413</v>
       </c>
       <c r="D371" t="n">
+        <v>1.397035112410701</v>
+      </c>
+      <c r="E371" t="n">
+        <v>1.38784831626961</v>
+      </c>
+      <c r="F371" t="n">
         <v>0.009186796141091413</v>
       </c>
     </row>
@@ -20807,6 +23037,12 @@
         <v>0.007249696676034006</v>
       </c>
       <c r="D372" t="n">
+        <v>-0.1789364629440676</v>
+      </c>
+      <c r="E372" t="n">
+        <v>-0.1861861596201016</v>
+      </c>
+      <c r="F372" t="n">
         <v>0.007249696676034006</v>
       </c>
     </row>
@@ -20825,6 +23061,12 @@
         <v>-0.005631726672502717</v>
       </c>
       <c r="D373" t="n">
+        <v>0.03882063203884516</v>
+      </c>
+      <c r="E373" t="n">
+        <v>0.04445235871134788</v>
+      </c>
+      <c r="F373" t="n">
         <v>0.005631726672502717</v>
       </c>
     </row>
@@ -20843,6 +23085,12 @@
         <v>-0.004751366260077772</v>
       </c>
       <c r="D374" t="n">
+        <v>-1.077036407086272</v>
+      </c>
+      <c r="E374" t="n">
+        <v>-1.072285040826195</v>
+      </c>
+      <c r="F374" t="n">
         <v>0.004751366260077772</v>
       </c>
     </row>
@@ -20861,6 +23109,12 @@
         <v>0.004718415970227291</v>
       </c>
       <c r="D375" t="n">
+        <v>-0.1037686928346489</v>
+      </c>
+      <c r="E375" t="n">
+        <v>-0.1084871088048762</v>
+      </c>
+      <c r="F375" t="n">
         <v>0.004718415970227291</v>
       </c>
     </row>
@@ -20879,6 +23133,12 @@
         <v>-0.0040482405067781</v>
       </c>
       <c r="D376" t="n">
+        <v>1.43200752007996</v>
+      </c>
+      <c r="E376" t="n">
+        <v>1.436055760586738</v>
+      </c>
+      <c r="F376" t="n">
         <v>0.0040482405067781</v>
       </c>
     </row>
@@ -20897,6 +23157,12 @@
         <v>0.002170739079070283</v>
       </c>
       <c r="D377" t="n">
+        <v>-0.6097559208811891</v>
+      </c>
+      <c r="E377" t="n">
+        <v>-0.6119266599602594</v>
+      </c>
+      <c r="F377" t="n">
         <v>0.002170739079070283</v>
       </c>
     </row>
@@ -20917,6 +23183,12 @@
       <c r="D378" t="n">
         <v>0</v>
       </c>
+      <c r="E378" t="n">
+        <v>0</v>
+      </c>
+      <c r="F378" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -20933,6 +23205,12 @@
         <v>0</v>
       </c>
       <c r="D379" t="n">
+        <v>0</v>
+      </c>
+      <c r="E379" t="n">
+        <v>0</v>
+      </c>
+      <c r="F379" t="n">
         <v>0</v>
       </c>
     </row>
